--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="1157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="1201">
   <si>
     <t xml:space="preserve">HilotSpa — Progress Summary</t>
   </si>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">If the node runs on a rented host it is no longer "localized at each branch". One paragraph: for evaluation, one node ran hosted so the panel and testers could reach it; the node software is identical either way.</t>
   </si>
   <si>
-    <t xml:space="preserve">Only needed for route B. Route A keeps the claim literally true, which is the strongest argument for it.</t>
+    <t xml:space="preserve">Only needed for route B. Route A keeps the claim literally true, which is the strongest argument for it. | 2026-09-12: no longer hypothetical. The system is DEPLOYED as a single cloud instance in Singapore, which a panelist can see from the URL. Frame it first: the cloud instance is the EVALUATION ENVIRONMENT, chosen so respondents and panelists can reach the system from their own devices; the branch-node design is demonstrated as a schema-enforced property (write authority partitioned by physical resource ownership), with one-node-per-branch described but not deployed within the study period.</t>
   </si>
   <si>
     <t xml:space="preserve">2.40</t>
@@ -1685,6 +1685,57 @@
     <t xml:space="preserve">Built and VERIFIED LIVE 2026-09-05 in Chrome via ?stt=server: a spoken sentence came back as "I want it on September 8th uh 3:30 p.m." - the "uh" is a speech artifact nobody types - and the conversation booked from it. WHY IT EXISTS: Chrome's SpeechRecognition sends audio to Google's own transcription service, a second route out of the building that Risk R16 never covered; this keeps a client's spoken symptoms in the same GCP project, region and terms as the assistant. It is an ADDITION, not a replacement - Chrome keeps recognition because it captions a sentence as it is heard (NFR#4), and Safari/Firefox, which had no microphone at all, now have one. ?stt=server and ?stt=browser force either path for testing and for demonstrating both at the defence.</t>
   </si>
   <si>
+    <t xml:space="preserve">0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deploy the full stack to AWS EC2 over HTTPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One t3.small in ap-southeast-1 running the same compose stack as the laptop: Caddy on 80/443 serving the ng build output and reverse-proxying /api/* to Spring, with backend, Postgres and n8n private to the Docker network. DuckDNS domain, Let's Encrypt certificate from the production endpoint.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liodoq + Claude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIVE 2026-09-11 at https://hilotspa.duckdns.org. Flyway applied all five migrations to a virgin database, so V2 (the double-booking exclusion constraint) is really in this schema. Seeder: 2 branches, 5 users, 3 therapists, 3 rooms, 10 services, 12 protocols. Login, CORS, the tap path, the fallback path and the assistant all verified from the public internet. Full record in claude/2026-09-11-aws-deployment-live.md. Root volume had to be grown 8 -&gt; 30 GB mid-build; EBS enforces a 6-hour cooldown between resizes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recover the development environment after the OneDrive deletion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The project folder was deleted when OneDrive was uninstalled, and OneDrive was full so nothing had synced. Re-cloned from git, recovered .env from a VS Code buffer, restored the six keys that copy was missing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only gitignored files were lost. The recovered .env was an older copy missing FLYWAY_ENABLED, DDL_AUTO, BOOKING_OPEN_HOUR, BOOKING_CLOSE_HOUR, SPA_HOURS and ASSISTANT_EXPOSE_DEBUG - the first two defaulting to false/update would have put the node back on auto-DDL and V2 would never have been applied. Boot then failed with SQL 28P01: POSTGRES_PASSWORD is only read when Postgres initialises an EMPTY data directory, so the surviving volume kept its original password. Fixed with ALTER USER inside the container rather than dropping the volume, preserving every test booking and assessment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit the working-copy fixes so the deployed server can build them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B128, B130 and the relative API base existed only in the laptop working copy; B131 only on the server. The AWS backend builds from git, so none of them were running.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Committed 2026-09-12: AssistantServiceImpl, seven controllers, api.config.ts, chat-build-context.js, the re-synced workflow JSON and deploy-frontend.ps1. LESSON: a fix that is not committed does not exist anywhere a deployment can reach. Three separate bugs were re-encountered live because of this.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First outside-tester pass on the live site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A person outside the team used https://hilotspa.duckdns.org cold: registered, browsed, attempted a booking.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One tester, five minutes, one Major defect on the primary path (B133) that a week of self-testing missed - because the team always tests with accounts that already exist and profiles that are already cached. Record who tested, what they tapped and what happened; those notes are Chapter IV usability findings and are only free to collect while it is happening.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HilotSpa — Bug &amp; Finding Log</t>
   </si>
   <si>
@@ -3198,6 +3249,87 @@
   </si>
   <si>
     <t xml:space="preserve">OBSERVED, NOT YET DIAGNOSED - it may be correct behaviour badly worded. If only the 90 was open at that hour then offering it is right; what is missing is the sentence saying so. Check whether the 60 was genuinely unavailable at Tue 8 Sep 3:30 PM before treating this as a defect. If it was available, the assistant changed the client's order, which is a different and more serious thing. The duration IS stated in the reply, so nobody was misled about what they booked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssistantServiceImpl.bookableSlots / the OPEN TIMES panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every day chip read "2 times" - 9:00 AM and mid-afternoon - for a treatment whose real calendar holds twenty-odd openings a day. bookableSlots gives the FOCUSED treatment its whole calendar and every other treatment a cheap two-a-day sample. The browser draws the panel from that same list and focuses whichever treatment the REPLY named, so a client who TYPED or SPOKE the treatment name (rather than tapping a chip, which sends the focus with the message) always saw the sample. The times existed; the client was never shown them. Same false answer as B89, by a different route. The voice path can only type, so it always hit this.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed (VERIFIED LIVE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed 2026-09-11 with refocus() on the main ChatResponse return - recomputes the calendar for the treatment the reply settled on. One extra availability query and, because it runs AFTER the model call, zero extra tokens. Deliberately NOT applied to the hold-recovery return: the focused calendar is capped at 140 from the start of the window while the sample deliberately reaches day 7, so refocusing there could drop the very slot being confirmed. VERIFIED on AWS 2026-09-12: day chips read 18/27/27/14 times.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n Shape reply Code node + hilotspa-chat.workflow.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The client saw - and the text-to-speech READ ALOUD - the raw envelope: ...90 minutes?","book":false,"slotId":null,"serviceId":null}. The agent returned its JSON with the opening {"reply":" already stripped, so indexOf("{") was -1, JSON.parse failed, and the node handed the raw text straight through. The fix for exactly this (salvageReply, which cuts the sentence where the envelope resumes and returns NOTHING rather than debris) had been written into chat-shape-reply.js and NEVER PASTED INTO N8N.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found 2026-09-11 by diffing every Code node against its repo file: Build context matched exactly, Shape reply was 2,703 chars against 4,421 on disk. Worse, the 2026-09-05 re-export (task 0.16) had exported the STALE node, so the committed workflow JSON carried the bug too and re-importing would not have helped. Both Code nodes in the JSON are now byte-identical to their .js files. LESSON: a repo file and a running node are two different things, and an export captures the running one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssistantServiceImpl.myBookingSummaries + prompt rule 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asked "what are my bookings", the assistant transcribed the internal MY BOOKINGS block verbatim: markdown * bullets that nothing renders and the TTS speaks as noise, raw enum values CONFIRMED and NO_SHOW, and every visit back to six days earlier all described as "current". On the 9th exactly one visit was still upcoming. Rule 14 said WHERE to answer from and never HOW, so the model did the literal thing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed (prompt half verified live)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed 2026-09-11 in two places. Java: myBookingSummaries splits still-to-come from already-happened, sorts soonest first, caps at six, and runs the status through sayStatus() so a client hears "missed" rather than "NO_SHOW" - the reply is read out loud, and NO_SHOW is a database column value, not a word to say to a person. Prompt: rule 14a (read the list, never recite it; one or two sentences; the labels are for the agent) and 14b (no asterisks, bullets, numbering or headings, in either language). Prompt half verified on AWS 2026-09-12 - the reply named the existing booking in prose with no markup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven controllers @CrossOrigin + SecurityConfig CorsConfigurationSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The first login from the deployed site returned 403, not 401 - the request was refused before the password was ever read. Two independent causes, both hardcoding the dev origin. (1) .env still said FRONTEND_ORIGIN=http://localhost:4200, which SecurityConfig feeds to setAllowedOrigins; there is no AuthController among the annotated classes so login goes through that bean, and this alone was the 403. (2) B31, open since Session 3: seven controllers carrying @CrossOrigin(origins="http://localhost:4200"), so fixing only the .env would have let the client log in and then failed on the very next request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proved 2026-09-11 with two curls from inside the server, bypassing Caddy: no-origin 200, with-origin 403. Browsers send Origin on POST EVEN SAME-ORIGIN, so this could never appear under ng serve where the allowed origin and the real origin happened to be the same string. Fixed by setting the real origin and deleting all seven annotations plus their imports, leaving the bean as the single source of truth. AssistantController already carried a comment saying precisely this. WORTH A PAPER LINE: the annotation and the bean were two expressions of one policy and they agreed exactly until the first real deployment, which is the only event that could ever have told them apart.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pages/book/book.ts confirmSlot + the send() tail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A hold the assistant settled in prose is sometimes discarded, leaving the client told a time is held with no button anywhere to take it. confirmSlot opens with "if (!id || this.confirming() || this.thinking()) return;" - a SILENT return, no message and no card - and send() clears pendingOpen immediately BEFORE calling it, so the slot is gone. Hard to hit while typing (one turn at a time); on the voice path SpeechRecognition can deliver a final result and fire send() while the previous turn is still settling. Reported as "it only changes if I say I confirm the booking", i.e. failure depends on HOW it was said rather than WHAT was said.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open (diagnosed, not reproduced under observation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found 2026-09-12 by reading the code after a wrong first hypothesis (that send() cleared picked - it does not; picked is cleared in only six places, none of them in send). NOT YET CONFIRMED: the deciding observation is whether the READY TO BOOK card appears at all after a spoken "I confirm", or appears and then vanishes. Those have different causes. Proposed fix regardless: confirmSlot should report whether it opened, send() should keep pendingOpen when it did not, and a no-op on the one control that books a visit must never be silent. Workaround for the demo: typing "I confirm the booking" reliably produces the card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pages/service-detail book() + core/catalogue.store.ts load()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A client who registered, was signed in, and tapped "Book this" was sent to the REGISTER page. book() asked cat.anonymous() - which describes how the MENU was fetched, not who is reading it. Underneath: load() returns early while loaded() is true, and loadPublic() sets loaded=true, so once a visitor has browsed the menu the token is never consulted again for the rest of the session. force and clear() were both written for exactly this case and neither was ever called by anything. The button was the mild half: a signed-in client kept being served the PUBLIC menu, whose entries all carry suitable=true because nothing was judged - while the service page tells them it "says plainly whether this treatment is advised for you". A claim about a judgement that was never made, which is the B91 class of untruth the store's own comment warns about.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found 2026-09-15 by a real client (Keneth) on the LIVE site, on the primary path, within five minutes - a defect neither Liodoq nor Claude hit in a week, because both had accounts with demographics already cached. This is the argument for task 4.5 in miniature. Fixed in two places: book() now asks auth.token(); CatalogueStore gained a constructor effect that clears the cache whenever the token changes (invalidate only, never re-fetch - every screen calls load() on init and an effect firing requests on a token change becomes a mystery double-load later). LESSON, general: a cached view of the world must be invalidated when identity changes, or every "is this suitable for you?" on screen is about a different person than the one reading it.</t>
   </si>
   <si>
     <t xml:space="preserve">HilotSpa — Defense Risk Register</t>
@@ -3504,9 +3636,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -3638,7 +3771,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3663,11 +3796,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3675,11 +3808,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3687,7 +3820,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3705,6 +3838,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -3949,34 +4086,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -4122,7 +4259,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="14"/>
@@ -4167,11 +4304,11 @@
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">COUNTIF(Tasks!$A$5:$A$400,$A5)</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$400,$A5,Tasks!$E$5:$E$400,"Done")</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">COUNTIFS(Tasks!$A$5:$A$400,$A5,Tasks!$E$5:$E$400,"In Progress")</f>
@@ -4187,7 +4324,7 @@
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">IFERROR($C5/$B5,0)</f>
-        <v>0.807692307692308</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4312,11 +4449,11 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">SUM(B5:B9)</f>
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUM(C5:C9)</f>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D5:D9)</f>
@@ -4332,7 +4469,7 @@
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">IFERROR($C10/$B10,0)</f>
-        <v>0.734848484848485</v>
+        <v>0.742647058823529</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4369,8 +4506,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G140"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
@@ -4450,7 +4587,7 @@
       <c r="D6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -4473,7 +4610,7 @@
       <c r="D7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="6" t="s">
@@ -4496,7 +4633,7 @@
       <c r="D8" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="6" t="s">
@@ -4519,7 +4656,7 @@
       <c r="D9" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -4542,7 +4679,7 @@
       <c r="D10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="6" t="s">
@@ -4565,7 +4702,7 @@
       <c r="D11" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="6" t="s">
@@ -4588,7 +4725,7 @@
       <c r="D12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F12" s="6" t="s">
@@ -4632,7 +4769,7 @@
       <c r="D14" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="6"/>
@@ -4653,7 +4790,7 @@
       <c r="D15" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="6"/>
@@ -4674,7 +4811,7 @@
       <c r="D16" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="6"/>
@@ -4695,7 +4832,7 @@
       <c r="D17" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="6"/>
@@ -4716,7 +4853,7 @@
       <c r="D18" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="6"/>
@@ -4737,7 +4874,7 @@
       <c r="D19" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="6"/>
@@ -4779,7 +4916,7 @@
       <c r="D21" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F21" s="6"/>
@@ -4800,7 +4937,7 @@
       <c r="D22" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F22" s="6"/>
@@ -4821,7 +4958,7 @@
       <c r="D23" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F23" s="6"/>
@@ -4842,7 +4979,7 @@
       <c r="D24" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F24" s="6"/>
@@ -4863,7 +5000,7 @@
       <c r="D25" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F25" s="6"/>
@@ -4884,7 +5021,7 @@
       <c r="D26" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F26" s="6"/>
@@ -4905,7 +5042,7 @@
       <c r="D27" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F27" s="6"/>
@@ -4947,7 +5084,7 @@
       <c r="D29" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F29" s="6"/>
@@ -4966,7 +5103,7 @@
       <c r="D30" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="6"/>
@@ -4987,7 +5124,7 @@
       <c r="D31" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="17" t="s">
         <v>5</v>
       </c>
       <c r="F31" s="6"/>
@@ -5008,7 +5145,7 @@
       <c r="D32" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="17" t="s">
         <v>5</v>
       </c>
       <c r="F32" s="6"/>
@@ -5029,7 +5166,7 @@
       <c r="D33" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="17" t="s">
         <v>5</v>
       </c>
       <c r="F33" s="6"/>
@@ -5050,7 +5187,7 @@
       <c r="D34" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F34" s="6"/>
@@ -5071,7 +5208,7 @@
       <c r="D35" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="17" t="s">
         <v>5</v>
       </c>
       <c r="F35" s="6"/>
@@ -5092,7 +5229,7 @@
       <c r="D36" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F36" s="6"/>
@@ -5113,7 +5250,7 @@
       <c r="D37" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="6"/>
@@ -5155,7 +5292,7 @@
       <c r="D39" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F39" s="6"/>
@@ -5174,7 +5311,7 @@
       <c r="D40" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F40" s="6"/>
@@ -5195,7 +5332,7 @@
       <c r="D41" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F41" s="6"/>
@@ -5216,7 +5353,7 @@
       <c r="D42" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F42" s="6"/>
@@ -5235,7 +5372,7 @@
       <c r="D43" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="6"/>
@@ -5254,17 +5391,17 @@
       <c r="D44" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="16"/>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="19" t="s">
         <v>184</v>
       </c>
       <c r="C45" s="14" t="s">
@@ -5273,10 +5410,10 @@
       <c r="D45" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G45" s="14" t="s">
@@ -5284,10 +5421,10 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="19" t="s">
         <v>188</v>
       </c>
       <c r="C46" s="14" t="s">
@@ -5296,10 +5433,10 @@
       <c r="D46" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G46" s="14" t="s">
@@ -5307,10 +5444,10 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="19" t="s">
         <v>192</v>
       </c>
       <c r="C47" s="14" t="s">
@@ -5319,10 +5456,10 @@
       <c r="D47" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G47" s="14" t="s">
@@ -5330,10 +5467,10 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="19" t="s">
         <v>196</v>
       </c>
       <c r="C48" s="14" t="s">
@@ -5342,10 +5479,10 @@
       <c r="D48" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E48" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F48" s="18" t="s">
+      <c r="F48" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G48" s="14" t="s">
@@ -5353,10 +5490,10 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="19" t="s">
         <v>200</v>
       </c>
       <c r="C49" s="14" t="s">
@@ -5365,10 +5502,10 @@
       <c r="D49" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F49" s="18" t="s">
+      <c r="F49" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G49" s="14" t="s">
@@ -5376,10 +5513,10 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="19" t="s">
         <v>204</v>
       </c>
       <c r="C50" s="14" t="s">
@@ -5388,10 +5525,10 @@
       <c r="D50" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="E50" s="18" t="s">
+      <c r="E50" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F50" s="18" t="s">
+      <c r="F50" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G50" s="14" t="s">
@@ -5399,10 +5536,10 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="19" t="s">
         <v>208</v>
       </c>
       <c r="C51" s="14" t="s">
@@ -5411,10 +5548,10 @@
       <c r="D51" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F51" s="18" t="s">
+      <c r="F51" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G51" s="14" t="s">
@@ -5422,10 +5559,10 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B52" s="18" t="s">
+      <c r="B52" s="19" t="s">
         <v>212</v>
       </c>
       <c r="C52" s="14" t="s">
@@ -5434,10 +5571,10 @@
       <c r="D52" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="E52" s="18" t="s">
+      <c r="E52" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F52" s="18" t="s">
+      <c r="F52" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G52" s="14" t="s">
@@ -5445,10 +5582,10 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="19" t="s">
         <v>216</v>
       </c>
       <c r="C53" s="14" t="s">
@@ -5457,10 +5594,10 @@
       <c r="D53" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F53" s="18" t="s">
+      <c r="F53" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G53" s="14" t="s">
@@ -5468,10 +5605,10 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="19" t="s">
         <v>220</v>
       </c>
       <c r="C54" s="14" t="s">
@@ -5480,10 +5617,10 @@
       <c r="D54" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="E54" s="18" t="s">
+      <c r="E54" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F54" s="18" t="s">
+      <c r="F54" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G54" s="14" t="s">
@@ -5491,10 +5628,10 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="19" t="s">
         <v>224</v>
       </c>
       <c r="C55" s="14" t="s">
@@ -5503,10 +5640,10 @@
       <c r="D55" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E55" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F55" s="18" t="s">
+      <c r="F55" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G55" s="14" t="s">
@@ -5514,10 +5651,10 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B56" s="18" t="s">
+      <c r="B56" s="19" t="s">
         <v>228</v>
       </c>
       <c r="C56" s="14" t="s">
@@ -5526,10 +5663,10 @@
       <c r="D56" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="E56" s="18" t="s">
+      <c r="E56" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F56" s="18" t="s">
+      <c r="F56" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G56" s="14" t="s">
@@ -5537,10 +5674,10 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B57" s="18" t="s">
+      <c r="B57" s="19" t="s">
         <v>232</v>
       </c>
       <c r="C57" s="14" t="s">
@@ -5549,10 +5686,10 @@
       <c r="D57" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E57" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="18" t="s">
+      <c r="F57" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G57" s="14" t="s">
@@ -5560,10 +5697,10 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="18" t="s">
+      <c r="B58" s="19" t="s">
         <v>236</v>
       </c>
       <c r="C58" s="14" t="s">
@@ -5572,10 +5709,10 @@
       <c r="D58" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="E58" s="18" t="s">
+      <c r="E58" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F58" s="18" t="s">
+      <c r="F58" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G58" s="14" t="s">
@@ -5583,10 +5720,10 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B59" s="18" t="s">
+      <c r="B59" s="19" t="s">
         <v>240</v>
       </c>
       <c r="C59" s="14" t="s">
@@ -5595,10 +5732,10 @@
       <c r="D59" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F59" s="18" t="s">
+      <c r="F59" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G59" s="14" t="s">
@@ -5606,10 +5743,10 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B60" s="18" t="s">
+      <c r="B60" s="19" t="s">
         <v>244</v>
       </c>
       <c r="C60" s="14" t="s">
@@ -5618,10 +5755,10 @@
       <c r="D60" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="E60" s="18" t="s">
+      <c r="E60" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F60" s="18" t="s">
+      <c r="F60" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G60" s="14" t="s">
@@ -5629,10 +5766,10 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="17" t="s">
+      <c r="A61" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B61" s="18" t="s">
+      <c r="B61" s="19" t="s">
         <v>248</v>
       </c>
       <c r="C61" s="14" t="s">
@@ -5641,10 +5778,10 @@
       <c r="D61" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="E61" s="18" t="s">
+      <c r="E61" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F61" s="18" t="s">
+      <c r="F61" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G61" s="14" t="s">
@@ -5652,10 +5789,10 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="19" t="s">
         <v>252</v>
       </c>
       <c r="C62" s="14" t="s">
@@ -5664,10 +5801,10 @@
       <c r="D62" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="E62" s="18" t="s">
+      <c r="E62" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="18" t="s">
+      <c r="F62" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G62" s="14" t="s">
@@ -5675,10 +5812,10 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="19" t="s">
         <v>256</v>
       </c>
       <c r="C63" s="14" t="s">
@@ -5687,10 +5824,10 @@
       <c r="D63" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="E63" s="18" t="s">
+      <c r="E63" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F63" s="18" t="s">
+      <c r="F63" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G63" s="14" t="s">
@@ -5698,10 +5835,10 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="19" t="s">
         <v>260</v>
       </c>
       <c r="C64" s="14" t="s">
@@ -5710,10 +5847,10 @@
       <c r="D64" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="E64" s="18" t="s">
+      <c r="E64" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F64" s="18" t="s">
+      <c r="F64" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G64" s="14" t="s">
@@ -5721,10 +5858,10 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="19" t="s">
         <v>264</v>
       </c>
       <c r="C65" s="14" t="s">
@@ -5733,10 +5870,10 @@
       <c r="D65" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E65" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F65" s="18" t="s">
+      <c r="F65" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G65" s="14" t="s">
@@ -5744,10 +5881,10 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="17" t="s">
+      <c r="A66" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B66" s="18" t="s">
+      <c r="B66" s="19" t="s">
         <v>268</v>
       </c>
       <c r="C66" s="14" t="s">
@@ -5756,10 +5893,10 @@
       <c r="D66" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="E66" s="18" t="s">
+      <c r="E66" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F66" s="18" t="s">
+      <c r="F66" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G66" s="14" t="s">
@@ -5767,10 +5904,10 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="17" t="s">
+      <c r="A67" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B67" s="18" t="s">
+      <c r="B67" s="19" t="s">
         <v>272</v>
       </c>
       <c r="C67" s="14" t="s">
@@ -5779,10 +5916,10 @@
       <c r="D67" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="E67" s="18" t="s">
+      <c r="E67" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F67" s="18" t="s">
+      <c r="F67" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G67" s="14" t="s">
@@ -5790,10 +5927,10 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="17" t="s">
+      <c r="A68" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B68" s="18" t="s">
+      <c r="B68" s="19" t="s">
         <v>276</v>
       </c>
       <c r="C68" s="14" t="s">
@@ -5802,10 +5939,10 @@
       <c r="D68" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="E68" s="18" t="s">
+      <c r="E68" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F68" s="18" t="s">
+      <c r="F68" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G68" s="14" t="s">
@@ -5813,10 +5950,10 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B69" s="18" t="s">
+      <c r="B69" s="19" t="s">
         <v>280</v>
       </c>
       <c r="C69" s="14" t="s">
@@ -5825,10 +5962,10 @@
       <c r="D69" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="E69" s="18" t="s">
+      <c r="E69" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F69" s="18" t="s">
+      <c r="F69" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G69" s="14" t="s">
@@ -5836,10 +5973,10 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="17" t="s">
+      <c r="A70" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B70" s="18" t="s">
+      <c r="B70" s="19" t="s">
         <v>284</v>
       </c>
       <c r="C70" s="14" t="s">
@@ -5848,10 +5985,10 @@
       <c r="D70" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="E70" s="18" t="s">
+      <c r="E70" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F70" s="18" t="s">
+      <c r="F70" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G70" s="14" t="s">
@@ -5859,10 +5996,10 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B71" s="18" t="s">
+      <c r="B71" s="19" t="s">
         <v>288</v>
       </c>
       <c r="C71" s="14" t="s">
@@ -5871,10 +6008,10 @@
       <c r="D71" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="E71" s="18" t="s">
+      <c r="E71" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F71" s="18" t="s">
+      <c r="F71" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G71" s="14" t="s">
@@ -5882,10 +6019,10 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B72" s="18" t="s">
+      <c r="B72" s="19" t="s">
         <v>292</v>
       </c>
       <c r="C72" s="14" t="s">
@@ -5894,10 +6031,10 @@
       <c r="D72" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="E72" s="18" t="s">
+      <c r="E72" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F72" s="18" t="s">
+      <c r="F72" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G72" s="14" t="s">
@@ -5905,10 +6042,10 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="17" t="s">
+      <c r="A73" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B73" s="18" t="s">
+      <c r="B73" s="19" t="s">
         <v>296</v>
       </c>
       <c r="C73" s="14" t="s">
@@ -5917,10 +6054,10 @@
       <c r="D73" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="E73" s="18" t="s">
+      <c r="E73" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F73" s="18" t="s">
+      <c r="F73" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G73" s="14" t="s">
@@ -5928,10 +6065,10 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="17" t="s">
+      <c r="A74" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B74" s="18" t="s">
+      <c r="B74" s="19" t="s">
         <v>300</v>
       </c>
       <c r="C74" s="14" t="s">
@@ -5940,10 +6077,10 @@
       <c r="D74" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="E74" s="18" t="s">
+      <c r="E74" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F74" s="18" t="s">
+      <c r="F74" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G74" s="14" t="s">
@@ -5951,10 +6088,10 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B75" s="18" t="s">
+      <c r="B75" s="19" t="s">
         <v>304</v>
       </c>
       <c r="C75" s="14" t="s">
@@ -5963,10 +6100,10 @@
       <c r="D75" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="E75" s="18" t="s">
+      <c r="E75" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F75" s="18" t="s">
+      <c r="F75" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G75" s="14" t="s">
@@ -5974,10 +6111,10 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B76" s="18" t="s">
+      <c r="B76" s="19" t="s">
         <v>308</v>
       </c>
       <c r="C76" s="14" t="s">
@@ -5986,10 +6123,10 @@
       <c r="D76" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="E76" s="18" t="s">
+      <c r="E76" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F76" s="18" t="s">
+      <c r="F76" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G76" s="14" t="s">
@@ -5997,10 +6134,10 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="17" t="s">
+      <c r="A77" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B77" s="18" t="s">
+      <c r="B77" s="19" t="s">
         <v>312</v>
       </c>
       <c r="C77" s="14" t="s">
@@ -6009,10 +6146,10 @@
       <c r="D77" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="E77" s="18" t="s">
+      <c r="E77" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F77" s="18" t="s">
+      <c r="F77" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G77" s="14" t="s">
@@ -6020,10 +6157,10 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="17" t="s">
+      <c r="A78" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B78" s="18" t="s">
+      <c r="B78" s="19" t="s">
         <v>316</v>
       </c>
       <c r="C78" s="14" t="s">
@@ -6032,10 +6169,10 @@
       <c r="D78" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="E78" s="18" t="s">
+      <c r="E78" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F78" s="18" t="s">
+      <c r="F78" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G78" s="14" t="s">
@@ -6043,10 +6180,10 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="17" t="s">
+      <c r="A79" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B79" s="18" t="s">
+      <c r="B79" s="19" t="s">
         <v>320</v>
       </c>
       <c r="C79" s="14" t="s">
@@ -6055,10 +6192,10 @@
       <c r="D79" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="E79" s="18" t="s">
+      <c r="E79" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F79" s="18" t="s">
+      <c r="F79" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G79" s="14" t="s">
@@ -6066,10 +6203,10 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="17" t="s">
+      <c r="A80" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B80" s="18" t="s">
+      <c r="B80" s="19" t="s">
         <v>324</v>
       </c>
       <c r="C80" s="14" t="s">
@@ -6078,10 +6215,10 @@
       <c r="D80" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="E80" s="18" t="s">
+      <c r="E80" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F80" s="18" t="s">
+      <c r="F80" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G80" s="14" t="s">
@@ -6089,10 +6226,10 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="17" t="s">
+      <c r="A81" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="B81" s="19" t="s">
         <v>328</v>
       </c>
       <c r="C81" s="14" t="s">
@@ -6101,10 +6238,10 @@
       <c r="D81" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="E81" s="18" t="s">
+      <c r="E81" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F81" s="18" t="s">
+      <c r="F81" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G81" s="14" t="s">
@@ -6112,10 +6249,10 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="17" t="s">
+      <c r="A82" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B82" s="18" t="s">
+      <c r="B82" s="19" t="s">
         <v>332</v>
       </c>
       <c r="C82" s="14" t="s">
@@ -6124,10 +6261,10 @@
       <c r="D82" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="E82" s="18" t="s">
+      <c r="E82" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F82" s="18" t="s">
+      <c r="F82" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G82" s="14" t="s">
@@ -6135,10 +6272,10 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="17" t="s">
+      <c r="A83" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B83" s="18" t="s">
+      <c r="B83" s="19" t="s">
         <v>336</v>
       </c>
       <c r="C83" s="14" t="s">
@@ -6147,10 +6284,10 @@
       <c r="D83" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="E83" s="18" t="s">
+      <c r="E83" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F83" s="18" t="s">
+      <c r="F83" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G83" s="14" t="s">
@@ -6158,10 +6295,10 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="17" t="s">
+      <c r="A84" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B84" s="18" t="s">
+      <c r="B84" s="19" t="s">
         <v>340</v>
       </c>
       <c r="C84" s="14" t="s">
@@ -6170,10 +6307,10 @@
       <c r="D84" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="E84" s="18" t="s">
+      <c r="E84" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F84" s="18" t="s">
+      <c r="F84" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G84" s="14" t="s">
@@ -6181,10 +6318,10 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="17" t="s">
+      <c r="A85" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="B85" s="19" t="s">
         <v>344</v>
       </c>
       <c r="C85" s="14" t="s">
@@ -6193,10 +6330,10 @@
       <c r="D85" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="E85" s="18" t="s">
+      <c r="E85" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F85" s="18" t="s">
+      <c r="F85" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G85" s="14" t="s">
@@ -6204,10 +6341,10 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="17" t="s">
+      <c r="A86" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B86" s="18" t="s">
+      <c r="B86" s="19" t="s">
         <v>348</v>
       </c>
       <c r="C86" s="14" t="s">
@@ -6216,10 +6353,10 @@
       <c r="D86" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="E86" s="18" t="s">
+      <c r="E86" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="18" t="s">
+      <c r="F86" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G86" s="14" t="s">
@@ -6227,10 +6364,10 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="17" t="s">
+      <c r="A87" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B87" s="18" t="s">
+      <c r="B87" s="19" t="s">
         <v>352</v>
       </c>
       <c r="C87" s="14" t="s">
@@ -6239,10 +6376,10 @@
       <c r="D87" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="E87" s="18" t="s">
+      <c r="E87" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F87" s="18" t="s">
+      <c r="F87" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G87" s="14" t="s">
@@ -6250,10 +6387,10 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="17" t="s">
+      <c r="A88" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B88" s="18" t="s">
+      <c r="B88" s="19" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="14" t="s">
@@ -6262,10 +6399,10 @@
       <c r="D88" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="E88" s="18" t="s">
+      <c r="E88" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="18" t="s">
+      <c r="F88" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G88" s="14" t="s">
@@ -6273,10 +6410,10 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="17" t="s">
+      <c r="A89" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B89" s="18" t="s">
+      <c r="B89" s="19" t="s">
         <v>360</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -6285,10 +6422,10 @@
       <c r="D89" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="E89" s="18" t="s">
+      <c r="E89" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F89" s="18" t="s">
+      <c r="F89" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G89" s="14" t="s">
@@ -6296,10 +6433,10 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="17" t="s">
+      <c r="A90" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B90" s="18" t="s">
+      <c r="B90" s="19" t="s">
         <v>364</v>
       </c>
       <c r="C90" s="14" t="s">
@@ -6308,10 +6445,10 @@
       <c r="D90" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="E90" s="18" t="s">
+      <c r="E90" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F90" s="18" t="s">
+      <c r="F90" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G90" s="14" t="s">
@@ -6319,10 +6456,10 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="17" t="s">
+      <c r="A91" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B91" s="18" t="s">
+      <c r="B91" s="19" t="s">
         <v>368</v>
       </c>
       <c r="C91" s="14" t="s">
@@ -6331,10 +6468,10 @@
       <c r="D91" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="E91" s="18" t="s">
+      <c r="E91" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F91" s="18" t="s">
+      <c r="F91" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G91" s="14" t="s">
@@ -6342,10 +6479,10 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="17" t="s">
+      <c r="A92" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B92" s="18" t="s">
+      <c r="B92" s="19" t="s">
         <v>372</v>
       </c>
       <c r="C92" s="14" t="s">
@@ -6354,10 +6491,10 @@
       <c r="D92" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="E92" s="18" t="s">
+      <c r="E92" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F92" s="18" t="s">
+      <c r="F92" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G92" s="14" t="s">
@@ -6365,10 +6502,10 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="17" t="s">
+      <c r="A93" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B93" s="18" t="s">
+      <c r="B93" s="19" t="s">
         <v>376</v>
       </c>
       <c r="C93" s="14" t="s">
@@ -6377,10 +6514,10 @@
       <c r="D93" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="E93" s="18" t="s">
+      <c r="E93" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F93" s="18" t="s">
+      <c r="F93" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G93" s="14" t="s">
@@ -6388,10 +6525,10 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="17" t="s">
+      <c r="A94" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B94" s="18" t="s">
+      <c r="B94" s="19" t="s">
         <v>380</v>
       </c>
       <c r="C94" s="14" t="s">
@@ -6400,10 +6537,10 @@
       <c r="D94" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="E94" s="18" t="s">
+      <c r="E94" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="18" t="s">
+      <c r="F94" s="19" t="s">
         <v>50</v>
       </c>
       <c r="G94" s="14" t="s">
@@ -6411,10 +6548,10 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="17" t="s">
+      <c r="A95" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B95" s="18" t="s">
+      <c r="B95" s="19" t="s">
         <v>384</v>
       </c>
       <c r="C95" s="14" t="s">
@@ -6423,10 +6560,10 @@
       <c r="D95" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="E95" s="18" t="s">
+      <c r="E95" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F95" s="18" t="s">
+      <c r="F95" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G95" s="14" t="s">
@@ -6434,10 +6571,10 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="17" t="s">
+      <c r="A96" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B96" s="18" t="s">
+      <c r="B96" s="19" t="s">
         <v>388</v>
       </c>
       <c r="C96" s="14" t="s">
@@ -6446,10 +6583,10 @@
       <c r="D96" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="E96" s="18" t="s">
+      <c r="E96" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F96" s="18" t="s">
+      <c r="F96" s="19" t="s">
         <v>28</v>
       </c>
       <c r="G96" s="14" t="s">
@@ -6457,10 +6594,10 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="17" t="s">
+      <c r="A97" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B97" s="18" t="s">
+      <c r="B97" s="19" t="s">
         <v>392</v>
       </c>
       <c r="C97" s="14" t="s">
@@ -6469,10 +6606,10 @@
       <c r="D97" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="E97" s="18" t="s">
+      <c r="E97" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F97" s="18" t="s">
+      <c r="F97" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G97" s="14" t="s">
@@ -6480,10 +6617,10 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="17" t="s">
+      <c r="A98" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B98" s="18" t="s">
+      <c r="B98" s="19" t="s">
         <v>396</v>
       </c>
       <c r="C98" s="14" t="s">
@@ -6492,10 +6629,10 @@
       <c r="D98" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="E98" s="18" t="s">
+      <c r="E98" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F98" s="18" t="s">
+      <c r="F98" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G98" s="14" t="s">
@@ -6503,10 +6640,10 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="17" t="s">
+      <c r="A99" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B99" s="18" t="s">
+      <c r="B99" s="19" t="s">
         <v>400</v>
       </c>
       <c r="C99" s="14" t="s">
@@ -6515,10 +6652,10 @@
       <c r="D99" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="E99" s="18" t="s">
+      <c r="E99" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F99" s="18" t="s">
+      <c r="F99" s="19" t="s">
         <v>37</v>
       </c>
       <c r="G99" s="14" t="s">
@@ -6526,10 +6663,10 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="19" t="s">
+      <c r="A100" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B100" s="20" t="s">
+      <c r="B100" s="21" t="s">
         <v>404</v>
       </c>
       <c r="C100" s="16" t="s">
@@ -6538,10 +6675,10 @@
       <c r="D100" s="16" t="s">
         <v>406</v>
       </c>
-      <c r="E100" s="20" t="s">
+      <c r="E100" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F100" s="20" t="s">
+      <c r="F100" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G100" s="16" t="s">
@@ -6549,10 +6686,10 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="19" t="s">
+      <c r="A101" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B101" s="20" t="s">
+      <c r="B101" s="21" t="s">
         <v>408</v>
       </c>
       <c r="C101" s="16" t="s">
@@ -6561,10 +6698,10 @@
       <c r="D101" s="16" t="s">
         <v>410</v>
       </c>
-      <c r="E101" s="20" t="s">
+      <c r="E101" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F101" s="20" t="s">
+      <c r="F101" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G101" s="16" t="s">
@@ -6572,10 +6709,10 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="19" t="s">
+      <c r="A102" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B102" s="20" t="s">
+      <c r="B102" s="21" t="s">
         <v>412</v>
       </c>
       <c r="C102" s="16" t="s">
@@ -6584,10 +6721,10 @@
       <c r="D102" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="E102" s="20" t="s">
+      <c r="E102" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F102" s="20" t="s">
+      <c r="F102" s="21" t="s">
         <v>28</v>
       </c>
       <c r="G102" s="16" t="s">
@@ -6595,10 +6732,10 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="19" t="s">
+      <c r="A103" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B103" s="20" t="s">
+      <c r="B103" s="21" t="s">
         <v>416</v>
       </c>
       <c r="C103" s="16" t="s">
@@ -6607,10 +6744,10 @@
       <c r="D103" s="16" t="s">
         <v>418</v>
       </c>
-      <c r="E103" s="20" t="s">
+      <c r="E103" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F103" s="20" t="s">
+      <c r="F103" s="21" t="s">
         <v>28</v>
       </c>
       <c r="G103" s="16" t="s">
@@ -6618,10 +6755,10 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="19" t="s">
+      <c r="A104" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B104" s="20" t="s">
+      <c r="B104" s="21" t="s">
         <v>420</v>
       </c>
       <c r="C104" s="16" t="s">
@@ -6630,10 +6767,10 @@
       <c r="D104" s="16" t="s">
         <v>422</v>
       </c>
-      <c r="E104" s="20" t="s">
+      <c r="E104" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F104" s="20" t="s">
+      <c r="F104" s="21" t="s">
         <v>28</v>
       </c>
       <c r="G104" s="16" t="s">
@@ -6641,10 +6778,10 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="19" t="s">
+      <c r="A105" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B105" s="20" t="s">
+      <c r="B105" s="21" t="s">
         <v>424</v>
       </c>
       <c r="C105" s="16" t="s">
@@ -6653,10 +6790,10 @@
       <c r="D105" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="E105" s="20" t="s">
+      <c r="E105" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F105" s="20" t="s">
+      <c r="F105" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G105" s="16" t="s">
@@ -6664,10 +6801,10 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="19" t="s">
+      <c r="A106" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B106" s="20" t="s">
+      <c r="B106" s="21" t="s">
         <v>428</v>
       </c>
       <c r="C106" s="16" t="s">
@@ -6676,10 +6813,10 @@
       <c r="D106" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="E106" s="20" t="s">
+      <c r="E106" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F106" s="20" t="s">
+      <c r="F106" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G106" s="16" t="s">
@@ -6687,10 +6824,10 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="19" t="s">
+      <c r="A107" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B107" s="20" t="s">
+      <c r="B107" s="21" t="s">
         <v>432</v>
       </c>
       <c r="C107" s="16" t="s">
@@ -6699,10 +6836,10 @@
       <c r="D107" s="16" t="s">
         <v>434</v>
       </c>
-      <c r="E107" s="20" t="s">
+      <c r="E107" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F107" s="20" t="s">
+      <c r="F107" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G107" s="16" t="s">
@@ -6710,10 +6847,10 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="19" t="s">
+      <c r="A108" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B108" s="20" t="s">
+      <c r="B108" s="21" t="s">
         <v>436</v>
       </c>
       <c r="C108" s="16" t="s">
@@ -6722,10 +6859,10 @@
       <c r="D108" s="16" t="s">
         <v>438</v>
       </c>
-      <c r="E108" s="20" t="s">
+      <c r="E108" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F108" s="20" t="s">
+      <c r="F108" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G108" s="16" t="s">
@@ -6733,10 +6870,10 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="19" t="s">
+      <c r="A109" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B109" s="20" t="s">
+      <c r="B109" s="21" t="s">
         <v>440</v>
       </c>
       <c r="C109" s="16" t="s">
@@ -6745,10 +6882,10 @@
       <c r="D109" s="16" t="s">
         <v>442</v>
       </c>
-      <c r="E109" s="20" t="s">
+      <c r="E109" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F109" s="20" t="s">
+      <c r="F109" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G109" s="16" t="s">
@@ -6756,10 +6893,10 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="19" t="s">
+      <c r="A110" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B110" s="20" t="s">
+      <c r="B110" s="21" t="s">
         <v>444</v>
       </c>
       <c r="C110" s="16" t="s">
@@ -6768,10 +6905,10 @@
       <c r="D110" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="E110" s="20" t="s">
+      <c r="E110" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F110" s="20" t="s">
+      <c r="F110" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G110" s="16" t="s">
@@ -6779,10 +6916,10 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="19" t="s">
+      <c r="A111" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B111" s="20" t="s">
+      <c r="B111" s="21" t="s">
         <v>448</v>
       </c>
       <c r="C111" s="16" t="s">
@@ -6791,10 +6928,10 @@
       <c r="D111" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="E111" s="20" t="s">
+      <c r="E111" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F111" s="20" t="s">
+      <c r="F111" s="21" t="s">
         <v>28</v>
       </c>
       <c r="G111" s="16" t="s">
@@ -6802,10 +6939,10 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="19" t="s">
+      <c r="A112" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B112" s="20" t="s">
+      <c r="B112" s="21" t="s">
         <v>452</v>
       </c>
       <c r="C112" s="16" t="s">
@@ -6814,10 +6951,10 @@
       <c r="D112" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="E112" s="20" t="s">
+      <c r="E112" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F112" s="20" t="s">
+      <c r="F112" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G112" s="16" t="s">
@@ -6825,10 +6962,10 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="19" t="s">
+      <c r="A113" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B113" s="20" t="s">
+      <c r="B113" s="21" t="s">
         <v>456</v>
       </c>
       <c r="C113" s="16" t="s">
@@ -6837,10 +6974,10 @@
       <c r="D113" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="E113" s="20" t="s">
+      <c r="E113" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F113" s="20" t="s">
+      <c r="F113" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G113" s="16" t="s">
@@ -6848,10 +6985,10 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="19" t="s">
+      <c r="A114" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B114" s="20" t="s">
+      <c r="B114" s="21" t="s">
         <v>460</v>
       </c>
       <c r="C114" s="16" t="s">
@@ -6860,10 +6997,10 @@
       <c r="D114" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="E114" s="20" t="s">
+      <c r="E114" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F114" s="20" t="s">
+      <c r="F114" s="21" t="s">
         <v>28</v>
       </c>
       <c r="G114" s="16" t="s">
@@ -6871,10 +7008,10 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="19" t="s">
+      <c r="A115" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B115" s="20" t="s">
+      <c r="B115" s="21" t="s">
         <v>464</v>
       </c>
       <c r="C115" s="16" t="s">
@@ -6883,10 +7020,10 @@
       <c r="D115" s="16" t="s">
         <v>466</v>
       </c>
-      <c r="E115" s="20" t="s">
+      <c r="E115" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F115" s="20" t="s">
+      <c r="F115" s="21" t="s">
         <v>28</v>
       </c>
       <c r="G115" s="16" t="s">
@@ -6894,10 +7031,10 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="19" t="s">
+      <c r="A116" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B116" s="20" t="s">
+      <c r="B116" s="21" t="s">
         <v>468</v>
       </c>
       <c r="C116" s="16" t="s">
@@ -6906,10 +7043,10 @@
       <c r="D116" s="16" t="s">
         <v>470</v>
       </c>
-      <c r="E116" s="20" t="s">
+      <c r="E116" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F116" s="20" t="s">
+      <c r="F116" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G116" s="16" t="s">
@@ -6917,10 +7054,10 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="19" t="s">
+      <c r="A117" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B117" s="20" t="s">
+      <c r="B117" s="21" t="s">
         <v>472</v>
       </c>
       <c r="C117" s="16" t="s">
@@ -6929,10 +7066,10 @@
       <c r="D117" s="16" t="s">
         <v>474</v>
       </c>
-      <c r="E117" s="20" t="s">
+      <c r="E117" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F117" s="20" t="s">
+      <c r="F117" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G117" s="16" t="s">
@@ -6940,10 +7077,10 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="19" t="s">
+      <c r="A118" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B118" s="20" t="s">
+      <c r="B118" s="21" t="s">
         <v>476</v>
       </c>
       <c r="C118" s="16" t="s">
@@ -6952,10 +7089,10 @@
       <c r="D118" s="16" t="s">
         <v>478</v>
       </c>
-      <c r="E118" s="20" t="s">
+      <c r="E118" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F118" s="20" t="s">
+      <c r="F118" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G118" s="16" t="s">
@@ -6963,10 +7100,10 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="19" t="s">
+      <c r="A119" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B119" s="20" t="s">
+      <c r="B119" s="21" t="s">
         <v>480</v>
       </c>
       <c r="C119" s="16" t="s">
@@ -6975,10 +7112,10 @@
       <c r="D119" s="16" t="s">
         <v>482</v>
       </c>
-      <c r="E119" s="20" t="s">
+      <c r="E119" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F119" s="20" t="s">
+      <c r="F119" s="21" t="s">
         <v>28</v>
       </c>
       <c r="G119" s="16" t="s">
@@ -6986,10 +7123,10 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="19" t="s">
+      <c r="A120" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B120" s="20" t="s">
+      <c r="B120" s="21" t="s">
         <v>484</v>
       </c>
       <c r="C120" s="16" t="s">
@@ -6998,10 +7135,10 @@
       <c r="D120" s="16" t="s">
         <v>486</v>
       </c>
-      <c r="E120" s="20" t="s">
+      <c r="E120" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F120" s="20" t="s">
+      <c r="F120" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G120" s="16" t="s">
@@ -7009,10 +7146,10 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="19" t="s">
+      <c r="A121" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B121" s="20" t="s">
+      <c r="B121" s="21" t="s">
         <v>488</v>
       </c>
       <c r="C121" s="16" t="s">
@@ -7021,10 +7158,10 @@
       <c r="D121" s="16" t="s">
         <v>490</v>
       </c>
-      <c r="E121" s="20" t="s">
+      <c r="E121" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F121" s="20" t="s">
+      <c r="F121" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G121" s="16" t="s">
@@ -7032,10 +7169,10 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="19" t="s">
+      <c r="A122" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B122" s="20" t="s">
+      <c r="B122" s="21" t="s">
         <v>492</v>
       </c>
       <c r="C122" s="16" t="s">
@@ -7044,10 +7181,10 @@
       <c r="D122" s="16" t="s">
         <v>494</v>
       </c>
-      <c r="E122" s="20" t="s">
+      <c r="E122" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F122" s="20" t="s">
+      <c r="F122" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G122" s="16" t="s">
@@ -7055,10 +7192,10 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="19" t="s">
+      <c r="A123" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B123" s="20" t="s">
+      <c r="B123" s="21" t="s">
         <v>496</v>
       </c>
       <c r="C123" s="16" t="s">
@@ -7067,10 +7204,10 @@
       <c r="D123" s="16" t="s">
         <v>498</v>
       </c>
-      <c r="E123" s="20" t="s">
+      <c r="E123" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F123" s="20" t="s">
+      <c r="F123" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G123" s="16" t="s">
@@ -7078,10 +7215,10 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="19" t="s">
+      <c r="A124" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B124" s="20" t="s">
+      <c r="B124" s="21" t="s">
         <v>500</v>
       </c>
       <c r="C124" s="16" t="s">
@@ -7090,10 +7227,10 @@
       <c r="D124" s="16" t="s">
         <v>502</v>
       </c>
-      <c r="E124" s="20" t="s">
+      <c r="E124" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F124" s="20" t="s">
+      <c r="F124" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G124" s="16" t="s">
@@ -7101,10 +7238,10 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="19" t="s">
+      <c r="A125" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B125" s="20" t="s">
+      <c r="B125" s="21" t="s">
         <v>504</v>
       </c>
       <c r="C125" s="16" t="s">
@@ -7113,10 +7250,10 @@
       <c r="D125" s="16" t="s">
         <v>506</v>
       </c>
-      <c r="E125" s="20" t="s">
+      <c r="E125" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F125" s="20" t="s">
+      <c r="F125" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G125" s="16" t="s">
@@ -7124,10 +7261,10 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="19" t="s">
+      <c r="A126" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B126" s="20" t="s">
+      <c r="B126" s="21" t="s">
         <v>508</v>
       </c>
       <c r="C126" s="16" t="s">
@@ -7136,10 +7273,10 @@
       <c r="D126" s="16" t="s">
         <v>510</v>
       </c>
-      <c r="E126" s="20" t="s">
+      <c r="E126" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F126" s="20" t="s">
+      <c r="F126" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G126" s="16" t="s">
@@ -7147,10 +7284,10 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="19" t="s">
+      <c r="A127" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B127" s="20" t="s">
+      <c r="B127" s="21" t="s">
         <v>512</v>
       </c>
       <c r="C127" s="16" t="s">
@@ -7159,10 +7296,10 @@
       <c r="D127" s="16" t="s">
         <v>514</v>
       </c>
-      <c r="E127" s="20" t="s">
+      <c r="E127" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F127" s="20" t="s">
+      <c r="F127" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G127" s="16" t="s">
@@ -7170,10 +7307,10 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="19" t="s">
+      <c r="A128" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B128" s="20" t="s">
+      <c r="B128" s="21" t="s">
         <v>516</v>
       </c>
       <c r="C128" s="16" t="s">
@@ -7182,10 +7319,10 @@
       <c r="D128" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="E128" s="20" t="s">
+      <c r="E128" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F128" s="20" t="s">
+      <c r="F128" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G128" s="16" t="s">
@@ -7193,10 +7330,10 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="19" t="s">
+      <c r="A129" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B129" s="20" t="s">
+      <c r="B129" s="21" t="s">
         <v>520</v>
       </c>
       <c r="C129" s="16" t="s">
@@ -7205,10 +7342,10 @@
       <c r="D129" s="16" t="s">
         <v>522</v>
       </c>
-      <c r="E129" s="20" t="s">
+      <c r="E129" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F129" s="20" t="s">
+      <c r="F129" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G129" s="16" t="s">
@@ -7216,10 +7353,10 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="19" t="s">
+      <c r="A130" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B130" s="20" t="s">
+      <c r="B130" s="21" t="s">
         <v>524</v>
       </c>
       <c r="C130" s="16" t="s">
@@ -7228,10 +7365,10 @@
       <c r="D130" s="16" t="s">
         <v>526</v>
       </c>
-      <c r="E130" s="20" t="s">
+      <c r="E130" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F130" s="20" t="s">
+      <c r="F130" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G130" s="16" t="s">
@@ -7239,10 +7376,10 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="247.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="19" t="s">
+      <c r="A131" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B131" s="20" t="s">
+      <c r="B131" s="21" t="s">
         <v>528</v>
       </c>
       <c r="C131" s="16" t="s">
@@ -7251,10 +7388,10 @@
       <c r="D131" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="E131" s="20" t="s">
+      <c r="E131" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F131" s="20" t="s">
+      <c r="F131" s="21" t="s">
         <v>28</v>
       </c>
       <c r="G131" s="16" t="s">
@@ -7262,10 +7399,10 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="19" t="s">
+      <c r="A132" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B132" s="20" t="s">
+      <c r="B132" s="21" t="s">
         <v>532</v>
       </c>
       <c r="C132" s="16" t="s">
@@ -7274,10 +7411,10 @@
       <c r="D132" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="E132" s="20" t="s">
+      <c r="E132" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F132" s="20" t="s">
+      <c r="F132" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G132" s="16" t="s">
@@ -7285,10 +7422,10 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="19" t="s">
+      <c r="A133" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B133" s="20" t="s">
+      <c r="B133" s="21" t="s">
         <v>536</v>
       </c>
       <c r="C133" s="16" t="s">
@@ -7297,10 +7434,10 @@
       <c r="D133" s="16" t="s">
         <v>538</v>
       </c>
-      <c r="E133" s="20" t="s">
+      <c r="E133" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F133" s="20" t="s">
+      <c r="F133" s="21" t="s">
         <v>28</v>
       </c>
       <c r="G133" s="16" t="s">
@@ -7308,10 +7445,10 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="19" t="s">
+      <c r="A134" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B134" s="20" t="s">
+      <c r="B134" s="21" t="s">
         <v>540</v>
       </c>
       <c r="C134" s="16" t="s">
@@ -7320,10 +7457,10 @@
       <c r="D134" s="16" t="s">
         <v>542</v>
       </c>
-      <c r="E134" s="20" t="s">
+      <c r="E134" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F134" s="20" t="s">
+      <c r="F134" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G134" s="16" t="s">
@@ -7331,10 +7468,10 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="19" t="s">
+      <c r="A135" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B135" s="20" t="s">
+      <c r="B135" s="21" t="s">
         <v>544</v>
       </c>
       <c r="C135" s="16" t="s">
@@ -7343,21 +7480,21 @@
       <c r="D135" s="16" t="s">
         <v>546</v>
       </c>
-      <c r="E135" s="20" t="s">
+      <c r="E135" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F135" s="20" t="s">
+      <c r="F135" s="21" t="s">
         <v>28</v>
       </c>
       <c r="G135" s="16" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="19" t="s">
+    <row r="136" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B136" s="20" t="s">
+      <c r="B136" s="21" t="s">
         <v>548</v>
       </c>
       <c r="C136" s="16" t="s">
@@ -7366,14 +7503,106 @@
       <c r="D136" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="E136" s="20" t="s">
+      <c r="E136" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F136" s="20" t="s">
+      <c r="F136" s="21" t="s">
         <v>37</v>
       </c>
       <c r="G136" s="16" t="s">
         <v>551</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B137" s="21" t="s">
+        <v>552</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="D137" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="E137" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F137" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="G137" s="16" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="D138" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="E138" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F138" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="G138" s="16" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="C139" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="D139" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="E139" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F139" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G139" s="16" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="C140" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="D140" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="E140" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F140" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G140" s="16" t="s">
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -7411,8 +7640,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G136"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
@@ -7425,7 +7654,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7436,13 +7665,13 @@
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -7453,2917 +7682,3055 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>560</v>
+        <v>575</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>564</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>560</v>
+        <v>581</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>567</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>560</v>
+        <v>584</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>570</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>560</v>
+        <v>587</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>575</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>560</v>
+        <v>592</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>577</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>578</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>560</v>
-      </c>
       <c r="G9" s="16" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>582</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>560</v>
+        <v>599</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>585</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>560</v>
+        <v>602</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>588</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>589</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>560</v>
+      <c r="F12" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>593</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>560</v>
+        <v>610</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>597</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>560</v>
+        <v>614</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>599</v>
+        <v>616</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>601</v>
+        <v>618</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>602</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>560</v>
+        <v>619</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>603</v>
+        <v>620</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>604</v>
+        <v>621</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>606</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>560</v>
+        <v>623</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>610</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>560</v>
+        <v>627</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>614</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>615</v>
+        <v>631</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>632</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>600</v>
-      </c>
       <c r="C19" s="16" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>619</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>560</v>
+        <v>636</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>623</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>560</v>
+        <v>640</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>626</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>560</v>
+        <v>643</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>630</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>560</v>
+        <v>647</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>634</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>560</v>
+        <v>651</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>577</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>635</v>
+        <v>652</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>637</v>
+        <v>654</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>639</v>
+        <v>656</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>640</v>
+        <v>657</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>641</v>
+        <v>658</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>642</v>
+        <v>659</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>644</v>
+        <v>661</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>647</v>
+        <v>664</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>650</v>
+        <v>667</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>651</v>
+        <v>668</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>652</v>
+        <v>669</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="F30" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>659</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>560</v>
-      </c>
       <c r="G30" s="16" t="s">
-        <v>660</v>
+        <v>677</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>661</v>
+        <v>678</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>662</v>
+        <v>679</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>670</v>
+        <v>687</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>672</v>
+        <v>689</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>675</v>
+        <v>692</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>676</v>
+        <v>693</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>677</v>
+        <v>694</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>676</v>
+        <v>693</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>681</v>
+        <v>698</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>682</v>
+        <v>699</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="C36" s="16" t="s">
+        <v>696</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>700</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>702</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>703</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>704</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>706</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>707</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>708</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>709</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>711</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>591</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>712</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="s">
+        <v>714</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>645</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>715</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>716</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
+        <v>718</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>719</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>720</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="s">
+        <v>722</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>723</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>724</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>726</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>727</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>728</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="s">
+        <v>730</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>731</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>732</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="s">
+        <v>734</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>735</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>736</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="s">
+        <v>738</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>739</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>740</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="s">
+        <v>742</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>743</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>744</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="21" t="s">
+        <v>746</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>639</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>747</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="21" t="s">
+        <v>749</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>750</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="s">
+        <v>753</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>754</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>755</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21" t="s">
+        <v>757</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>758</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="21" t="s">
+        <v>761</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>727</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>762</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="21" t="s">
+        <v>764</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>765</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>766</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="21" t="s">
+        <v>768</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>769</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>770</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="21" t="s">
+        <v>772</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>773</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="21" t="s">
+        <v>776</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>765</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>777</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="21" t="s">
+        <v>779</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>780</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>781</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="21" t="s">
+        <v>783</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>784</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>785</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="21" t="s">
+        <v>787</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>788</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>789</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="21" t="s">
+        <v>791</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>792</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>793</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="21" t="s">
+        <v>795</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>796</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="21" t="s">
+        <v>799</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>800</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="21" t="s">
+        <v>803</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>804</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="21" t="s">
+        <v>807</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>808</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>809</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="21" t="s">
+        <v>811</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C65" s="21" t="s">
         <v>679</v>
       </c>
-      <c r="D36" s="16" t="s">
-        <v>683</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
-        <v>685</v>
-      </c>
-      <c r="B37" s="20" t="s">
+      <c r="D65" s="16" t="s">
+        <v>812</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>815</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>816</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="21" t="s">
+        <v>818</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>819</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>820</v>
+      </c>
+      <c r="E67" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="21" t="s">
+        <v>822</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>823</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>824</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F68" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="21" t="s">
+        <v>826</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>827</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>828</v>
+      </c>
+      <c r="E69" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="21" t="s">
+        <v>830</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>831</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>832</v>
+      </c>
+      <c r="E70" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F70" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="21" t="s">
+        <v>834</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>835</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>836</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="21" t="s">
+        <v>838</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>839</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="E72" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F72" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="21" t="s">
+        <v>842</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>843</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>844</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F73" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="21" t="s">
+        <v>846</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>784</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>847</v>
+      </c>
+      <c r="E74" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F74" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G74" s="16" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="21" t="s">
+        <v>849</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>850</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>851</v>
+      </c>
+      <c r="E75" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F75" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G75" s="16" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="21" t="s">
+        <v>853</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>854</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>855</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G76" s="16" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="21" t="s">
+        <v>857</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>858</v>
+      </c>
+      <c r="D77" s="16" t="s">
+        <v>859</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F77" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="G77" s="16" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="21" t="s">
+        <v>861</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>862</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>863</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>864</v>
+      </c>
+      <c r="E78" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F78" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="G78" s="16" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>862</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>867</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>868</v>
+      </c>
+      <c r="E79" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="21" t="s">
+        <v>870</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>871</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>872</v>
+      </c>
+      <c r="E80" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F80" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="21" t="s">
+        <v>874</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>875</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>876</v>
+      </c>
+      <c r="E81" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F81" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G81" s="16" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="21" t="s">
+        <v>878</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>879</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>880</v>
+      </c>
+      <c r="E82" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F82" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G82" s="16" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="21" t="s">
+        <v>882</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>883</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>884</v>
+      </c>
+      <c r="E83" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F83" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="21" t="s">
+        <v>886</v>
+      </c>
+      <c r="B84" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>887</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>888</v>
+      </c>
+      <c r="E84" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F84" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G84" s="16" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="21" t="s">
+        <v>890</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>891</v>
+      </c>
+      <c r="D85" s="16" t="s">
+        <v>892</v>
+      </c>
+      <c r="E85" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F85" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G85" s="16" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="21" t="s">
+        <v>894</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>895</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>896</v>
+      </c>
+      <c r="E86" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F86" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="21" t="s">
+        <v>898</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>899</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>900</v>
+      </c>
+      <c r="E87" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F87" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="21" t="s">
+        <v>902</v>
+      </c>
+      <c r="B88" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>903</v>
+      </c>
+      <c r="D88" s="16" t="s">
+        <v>904</v>
+      </c>
+      <c r="E88" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F88" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G88" s="16" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="21" t="s">
+        <v>906</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="C89" s="21" t="s">
+        <v>907</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>908</v>
+      </c>
+      <c r="E89" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F89" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="21" t="s">
+        <v>910</v>
+      </c>
+      <c r="B90" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>911</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>912</v>
+      </c>
+      <c r="E90" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F90" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G90" s="16" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="21" t="s">
+        <v>914</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>911</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>915</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F91" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G91" s="16" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="21" t="s">
+        <v>917</v>
+      </c>
+      <c r="B92" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C92" s="21" t="s">
+        <v>918</v>
+      </c>
+      <c r="D92" s="16" t="s">
+        <v>919</v>
+      </c>
+      <c r="E92" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F92" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G92" s="16" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="21" t="s">
+        <v>921</v>
+      </c>
+      <c r="B93" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C93" s="21" t="s">
+        <v>922</v>
+      </c>
+      <c r="D93" s="16" t="s">
+        <v>923</v>
+      </c>
+      <c r="E93" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F93" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G93" s="16" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="21" t="s">
+        <v>925</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C94" s="21" t="s">
+        <v>926</v>
+      </c>
+      <c r="D94" s="16" t="s">
+        <v>927</v>
+      </c>
+      <c r="E94" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F94" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G94" s="16" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="21" t="s">
+        <v>929</v>
+      </c>
+      <c r="B95" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C95" s="21" t="s">
+        <v>930</v>
+      </c>
+      <c r="D95" s="16" t="s">
+        <v>931</v>
+      </c>
+      <c r="E95" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F95" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G95" s="16" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="21" t="s">
+        <v>933</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>934</v>
+      </c>
+      <c r="D96" s="16" t="s">
+        <v>935</v>
+      </c>
+      <c r="E96" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F96" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G96" s="16" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="21" t="s">
+        <v>937</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="C97" s="21" t="s">
+        <v>938</v>
+      </c>
+      <c r="D97" s="16" t="s">
+        <v>939</v>
+      </c>
+      <c r="E97" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F97" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="G97" s="16" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="21" t="s">
+        <v>941</v>
+      </c>
+      <c r="B98" s="21" t="s">
+        <v>516</v>
+      </c>
+      <c r="C98" s="21" t="s">
+        <v>942</v>
+      </c>
+      <c r="D98" s="16" t="s">
+        <v>943</v>
+      </c>
+      <c r="E98" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F98" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G98" s="16" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="21" t="s">
+        <v>945</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>516</v>
+      </c>
+      <c r="C99" s="21" t="s">
+        <v>946</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>947</v>
+      </c>
+      <c r="E99" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F99" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G99" s="16" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="21" t="s">
+        <v>949</v>
+      </c>
+      <c r="B100" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="C100" s="21" t="s">
+        <v>950</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="E100" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F100" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G100" s="16" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="21" t="s">
+        <v>953</v>
+      </c>
+      <c r="B101" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C101" s="21" t="s">
+        <v>954</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>955</v>
+      </c>
+      <c r="E101" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F101" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G101" s="16" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="21" t="s">
+        <v>957</v>
+      </c>
+      <c r="B102" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C102" s="21" t="s">
+        <v>591</v>
+      </c>
+      <c r="D102" s="16" t="s">
+        <v>958</v>
+      </c>
+      <c r="E102" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F102" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="G102" s="16" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="21" t="s">
+        <v>960</v>
+      </c>
+      <c r="B103" s="21" t="s">
+        <v>617</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>961</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>962</v>
+      </c>
+      <c r="E103" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F103" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="G103" s="16" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="21" t="s">
+        <v>964</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C104" s="21" t="s">
+        <v>965</v>
+      </c>
+      <c r="D104" s="16" t="s">
+        <v>966</v>
+      </c>
+      <c r="E104" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F104" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G104" s="16" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="21" t="s">
+        <v>968</v>
+      </c>
+      <c r="B105" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C105" s="21" t="s">
+        <v>969</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>970</v>
+      </c>
+      <c r="E105" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F105" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G105" s="16" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="21" t="s">
+        <v>972</v>
+      </c>
+      <c r="B106" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C106" s="21" t="s">
+        <v>973</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>974</v>
+      </c>
+      <c r="E106" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F106" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G106" s="16" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="21" t="s">
+        <v>976</v>
+      </c>
+      <c r="B107" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C107" s="21" t="s">
+        <v>977</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>978</v>
+      </c>
+      <c r="E107" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F107" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G107" s="16" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="21" t="s">
+        <v>980</v>
+      </c>
+      <c r="B108" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C108" s="21" t="s">
+        <v>981</v>
+      </c>
+      <c r="D108" s="16" t="s">
+        <v>982</v>
+      </c>
+      <c r="E108" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F108" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G108" s="16" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="21" t="s">
+        <v>984</v>
+      </c>
+      <c r="B109" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="20" t="s">
-        <v>686</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>687</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G37" s="16" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
-        <v>689</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>690</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>691</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>692</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="G38" s="16" t="s">
+      <c r="C109" s="21" t="s">
+        <v>985</v>
+      </c>
+      <c r="D109" s="16" t="s">
+        <v>986</v>
+      </c>
+      <c r="E109" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F109" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G109" s="16" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="21" t="s">
+        <v>988</v>
+      </c>
+      <c r="B110" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C110" s="21" t="s">
+        <v>989</v>
+      </c>
+      <c r="D110" s="16" t="s">
+        <v>990</v>
+      </c>
+      <c r="E110" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F110" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G110" s="16" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="21" t="s">
+        <v>992</v>
+      </c>
+      <c r="B111" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="C111" s="21" t="s">
+        <v>993</v>
+      </c>
+      <c r="D111" s="16" t="s">
+        <v>994</v>
+      </c>
+      <c r="E111" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F111" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G111" s="16" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="21" t="s">
+        <v>996</v>
+      </c>
+      <c r="B112" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="C112" s="21" t="s">
+        <v>997</v>
+      </c>
+      <c r="D112" s="16" t="s">
+        <v>998</v>
+      </c>
+      <c r="E112" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F112" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G112" s="16" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="21" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B113" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C113" s="21" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E113" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F113" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G113" s="16" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="21" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B114" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="C114" s="21" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E114" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F114" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G114" s="16" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="21" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B115" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C115" s="21" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D115" s="16" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E115" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F115" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G115" s="16" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="21" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B116" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="C116" s="21" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D116" s="16" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E116" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F116" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G116" s="16" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="21" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B117" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C117" s="21" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D117" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E117" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F117" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G117" s="16" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="21" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B118" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C118" s="21" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D118" s="16" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E118" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F118" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G118" s="16" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="21" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B119" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="C119" s="21" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D119" s="16" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E119" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F119" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G119" s="16" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="21" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B120" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C120" s="21" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D120" s="16" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E120" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F120" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G120" s="16" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="21" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B121" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C121" s="21" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D121" s="16" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E121" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F121" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G121" s="16" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="21" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B122" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C122" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D122" s="16" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E122" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F122" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G122" s="16" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B123" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" s="21" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D123" s="16" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E123" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F123" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G123" s="16" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="21" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B124" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C124" s="21" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D124" s="16" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E124" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F124" s="21" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G124" s="16" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="21" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B125" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C125" s="21" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D125" s="16" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E125" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F125" s="21" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G125" s="16" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="21" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B126" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C126" s="21" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D126" s="16" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E126" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F126" s="21" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G126" s="16" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="21" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B127" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="C127" s="21" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D127" s="16" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E127" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F127" s="21" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G127" s="16" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="21" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B128" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="C128" s="21" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D128" s="16" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E128" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F128" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G128" s="16" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="21" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B129" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="C129" s="21" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D129" s="16" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E129" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F129" s="21" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G129" s="16" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="21" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B130" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C130" s="21" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D130" s="16" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E130" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="F130" s="21" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="20" t="s">
-        <v>694</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>574</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>695</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G39" s="16" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="20" t="s">
-        <v>697</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>628</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>698</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>699</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F40" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
-        <v>701</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>702</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>703</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="20" t="s">
-        <v>705</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>706</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>707</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F42" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="20" t="s">
-        <v>709</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>710</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>711</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="20" t="s">
-        <v>713</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>714</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>715</v>
-      </c>
-      <c r="E44" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F44" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G44" s="16" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20" t="s">
-        <v>717</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>718</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>719</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20" t="s">
-        <v>721</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>722</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>723</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F46" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G46" s="16" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="20" t="s">
-        <v>725</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>726</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>727</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G47" s="16" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="20" t="s">
-        <v>729</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>622</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>730</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G48" s="16" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="20" t="s">
-        <v>732</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>733</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>734</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="20" t="s">
-        <v>736</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>737</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>738</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G50" s="16" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="20" t="s">
-        <v>740</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>741</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>742</v>
-      </c>
-      <c r="E51" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F51" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G51" s="16" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="20" t="s">
-        <v>744</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>710</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>745</v>
-      </c>
-      <c r="E52" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F52" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="20" t="s">
-        <v>747</v>
-      </c>
-      <c r="B53" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>748</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>749</v>
-      </c>
-      <c r="E53" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F53" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G53" s="16" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="20" t="s">
-        <v>751</v>
-      </c>
-      <c r="B54" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C54" s="20" t="s">
-        <v>752</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>753</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="20" t="s">
-        <v>755</v>
-      </c>
-      <c r="B55" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C55" s="20" t="s">
-        <v>756</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>757</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F55" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="20" t="s">
-        <v>759</v>
-      </c>
-      <c r="B56" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>748</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>760</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F56" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G56" s="16" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="20" t="s">
-        <v>762</v>
-      </c>
-      <c r="B57" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C57" s="20" t="s">
-        <v>763</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>764</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F57" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G57" s="16" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="20" t="s">
-        <v>766</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C58" s="20" t="s">
-        <v>767</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>768</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F58" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="20" t="s">
-        <v>770</v>
-      </c>
-      <c r="B59" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C59" s="20" t="s">
-        <v>771</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>772</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F59" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="20" t="s">
-        <v>774</v>
-      </c>
-      <c r="B60" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>775</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>776</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F60" s="20" t="s">
-        <v>615</v>
-      </c>
-      <c r="G60" s="16" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="20" t="s">
-        <v>778</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>779</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>780</v>
-      </c>
-      <c r="E61" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F61" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="20" t="s">
-        <v>782</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>783</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>784</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F62" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G62" s="16" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="20" t="s">
-        <v>786</v>
-      </c>
-      <c r="B63" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="C63" s="20" t="s">
-        <v>787</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>788</v>
-      </c>
-      <c r="E63" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F63" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G63" s="16" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="20" t="s">
-        <v>790</v>
-      </c>
-      <c r="B64" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>791</v>
-      </c>
-      <c r="D64" s="16" t="s">
-        <v>792</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F64" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G64" s="16" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="20" t="s">
-        <v>794</v>
-      </c>
-      <c r="B65" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>662</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>795</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F65" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G65" s="16" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="20" t="s">
-        <v>797</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C66" s="20" t="s">
-        <v>798</v>
-      </c>
-      <c r="D66" s="16" t="s">
-        <v>799</v>
-      </c>
-      <c r="E66" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F66" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G66" s="16" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="20" t="s">
-        <v>801</v>
-      </c>
-      <c r="B67" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="C67" s="20" t="s">
-        <v>802</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>803</v>
-      </c>
-      <c r="E67" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F67" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="20" t="s">
-        <v>805</v>
-      </c>
-      <c r="B68" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="C68" s="20" t="s">
-        <v>806</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>807</v>
-      </c>
-      <c r="E68" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F68" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G68" s="16" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="20" t="s">
-        <v>809</v>
-      </c>
-      <c r="B69" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="20" t="s">
-        <v>810</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>811</v>
-      </c>
-      <c r="E69" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F69" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="20" t="s">
-        <v>813</v>
-      </c>
-      <c r="B70" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="C70" s="20" t="s">
-        <v>814</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>815</v>
-      </c>
-      <c r="E70" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F70" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G70" s="16" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="20" t="s">
-        <v>817</v>
-      </c>
-      <c r="B71" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="C71" s="20" t="s">
-        <v>818</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>819</v>
-      </c>
-      <c r="E71" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F71" s="20" t="s">
-        <v>615</v>
-      </c>
-      <c r="G71" s="16" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="20" t="s">
-        <v>821</v>
-      </c>
-      <c r="B72" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="C72" s="20" t="s">
-        <v>822</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>823</v>
-      </c>
-      <c r="E72" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F72" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G72" s="16" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="20" t="s">
-        <v>825</v>
-      </c>
-      <c r="B73" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="C73" s="20" t="s">
-        <v>826</v>
-      </c>
-      <c r="D73" s="16" t="s">
-        <v>827</v>
-      </c>
-      <c r="E73" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F73" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G73" s="16" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="20" t="s">
-        <v>829</v>
-      </c>
-      <c r="B74" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="C74" s="20" t="s">
-        <v>767</v>
-      </c>
-      <c r="D74" s="16" t="s">
-        <v>830</v>
-      </c>
-      <c r="E74" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F74" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G74" s="16" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="20" t="s">
-        <v>832</v>
-      </c>
-      <c r="B75" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="C75" s="20" t="s">
-        <v>833</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>834</v>
-      </c>
-      <c r="E75" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F75" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G75" s="16" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="20" t="s">
-        <v>836</v>
-      </c>
-      <c r="B76" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="C76" s="20" t="s">
-        <v>837</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>838</v>
-      </c>
-      <c r="E76" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F76" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G76" s="16" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="20" t="s">
-        <v>840</v>
-      </c>
-      <c r="B77" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="C77" s="20" t="s">
-        <v>841</v>
-      </c>
-      <c r="D77" s="16" t="s">
-        <v>842</v>
-      </c>
-      <c r="E77" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F77" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="G77" s="16" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="20" t="s">
-        <v>844</v>
-      </c>
-      <c r="B78" s="20" t="s">
-        <v>845</v>
-      </c>
-      <c r="C78" s="20" t="s">
-        <v>846</v>
-      </c>
-      <c r="D78" s="16" t="s">
-        <v>847</v>
-      </c>
-      <c r="E78" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F78" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="G78" s="16" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="20" t="s">
-        <v>849</v>
-      </c>
-      <c r="B79" s="20" t="s">
-        <v>845</v>
-      </c>
-      <c r="C79" s="20" t="s">
-        <v>850</v>
-      </c>
-      <c r="D79" s="16" t="s">
-        <v>851</v>
-      </c>
-      <c r="E79" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F79" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="G79" s="16" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="20" t="s">
-        <v>853</v>
-      </c>
-      <c r="B80" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="C80" s="20" t="s">
-        <v>854</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>855</v>
-      </c>
-      <c r="E80" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F80" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G80" s="16" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="20" t="s">
-        <v>857</v>
-      </c>
-      <c r="B81" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="C81" s="20" t="s">
-        <v>858</v>
-      </c>
-      <c r="D81" s="16" t="s">
-        <v>859</v>
-      </c>
-      <c r="E81" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F81" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G81" s="16" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="20" t="s">
-        <v>861</v>
-      </c>
-      <c r="B82" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="C82" s="20" t="s">
-        <v>862</v>
-      </c>
-      <c r="D82" s="16" t="s">
-        <v>863</v>
-      </c>
-      <c r="E82" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F82" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G82" s="16" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="20" t="s">
-        <v>865</v>
-      </c>
-      <c r="B83" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="C83" s="20" t="s">
-        <v>866</v>
-      </c>
-      <c r="D83" s="16" t="s">
-        <v>867</v>
-      </c>
-      <c r="E83" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F83" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G83" s="16" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="20" t="s">
-        <v>869</v>
-      </c>
-      <c r="B84" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="C84" s="20" t="s">
-        <v>870</v>
-      </c>
-      <c r="D84" s="16" t="s">
-        <v>871</v>
-      </c>
-      <c r="E84" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F84" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G84" s="16" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="20" t="s">
-        <v>873</v>
-      </c>
-      <c r="B85" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="C85" s="20" t="s">
-        <v>874</v>
-      </c>
-      <c r="D85" s="16" t="s">
-        <v>875</v>
-      </c>
-      <c r="E85" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F85" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G85" s="16" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="20" t="s">
-        <v>877</v>
-      </c>
-      <c r="B86" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="C86" s="20" t="s">
-        <v>878</v>
-      </c>
-      <c r="D86" s="16" t="s">
-        <v>879</v>
-      </c>
-      <c r="E86" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F86" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G86" s="16" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="20" t="s">
-        <v>881</v>
-      </c>
-      <c r="B87" s="20" t="s">
+      <c r="G130" s="16" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="21" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B131" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="C87" s="20" t="s">
-        <v>882</v>
-      </c>
-      <c r="D87" s="16" t="s">
-        <v>883</v>
-      </c>
-      <c r="E87" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F87" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G87" s="16" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="20" t="s">
-        <v>885</v>
-      </c>
-      <c r="B88" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="C88" s="20" t="s">
-        <v>886</v>
-      </c>
-      <c r="D88" s="16" t="s">
-        <v>887</v>
-      </c>
-      <c r="E88" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F88" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G88" s="16" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="20" t="s">
-        <v>889</v>
-      </c>
-      <c r="B89" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="C89" s="20" t="s">
-        <v>890</v>
-      </c>
-      <c r="D89" s="16" t="s">
-        <v>891</v>
-      </c>
-      <c r="E89" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F89" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="G89" s="16" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="20" t="s">
-        <v>893</v>
-      </c>
-      <c r="B90" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="C90" s="20" t="s">
-        <v>894</v>
-      </c>
-      <c r="D90" s="16" t="s">
-        <v>895</v>
-      </c>
-      <c r="E90" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F90" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G90" s="16" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="20" t="s">
-        <v>897</v>
-      </c>
-      <c r="B91" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="C91" s="20" t="s">
-        <v>894</v>
-      </c>
-      <c r="D91" s="16" t="s">
-        <v>898</v>
-      </c>
-      <c r="E91" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F91" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G91" s="16" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="20" t="s">
-        <v>900</v>
-      </c>
-      <c r="B92" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C92" s="20" t="s">
-        <v>901</v>
-      </c>
-      <c r="D92" s="16" t="s">
-        <v>902</v>
-      </c>
-      <c r="E92" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F92" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G92" s="16" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="20" t="s">
-        <v>904</v>
-      </c>
-      <c r="B93" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="C93" s="20" t="s">
-        <v>905</v>
-      </c>
-      <c r="D93" s="16" t="s">
-        <v>906</v>
-      </c>
-      <c r="E93" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F93" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G93" s="16" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="20" t="s">
-        <v>908</v>
-      </c>
-      <c r="B94" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="C94" s="20" t="s">
-        <v>909</v>
-      </c>
-      <c r="D94" s="16" t="s">
-        <v>910</v>
-      </c>
-      <c r="E94" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F94" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G94" s="16" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="20" t="s">
-        <v>912</v>
-      </c>
-      <c r="B95" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>913</v>
-      </c>
-      <c r="D95" s="16" t="s">
-        <v>914</v>
-      </c>
-      <c r="E95" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F95" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G95" s="16" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="20" t="s">
-        <v>916</v>
-      </c>
-      <c r="B96" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C96" s="20" t="s">
-        <v>917</v>
-      </c>
-      <c r="D96" s="16" t="s">
-        <v>918</v>
-      </c>
-      <c r="E96" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F96" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G96" s="16" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="20" t="s">
-        <v>920</v>
-      </c>
-      <c r="B97" s="20" t="s">
-        <v>400</v>
-      </c>
-      <c r="C97" s="20" t="s">
-        <v>921</v>
-      </c>
-      <c r="D97" s="16" t="s">
-        <v>922</v>
-      </c>
-      <c r="E97" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F97" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="G97" s="16" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="20" t="s">
-        <v>924</v>
-      </c>
-      <c r="B98" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="C98" s="20" t="s">
-        <v>925</v>
-      </c>
-      <c r="D98" s="16" t="s">
-        <v>926</v>
-      </c>
-      <c r="E98" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F98" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G98" s="16" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="20" t="s">
-        <v>928</v>
-      </c>
-      <c r="B99" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="C99" s="20" t="s">
-        <v>929</v>
-      </c>
-      <c r="D99" s="16" t="s">
-        <v>930</v>
-      </c>
-      <c r="E99" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F99" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G99" s="16" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="20" t="s">
-        <v>932</v>
-      </c>
-      <c r="B100" s="20" t="s">
-        <v>500</v>
-      </c>
-      <c r="C100" s="20" t="s">
-        <v>933</v>
-      </c>
-      <c r="D100" s="16" t="s">
-        <v>934</v>
-      </c>
-      <c r="E100" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F100" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G100" s="16" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="20" t="s">
-        <v>936</v>
-      </c>
-      <c r="B101" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C101" s="20" t="s">
-        <v>937</v>
-      </c>
-      <c r="D101" s="16" t="s">
-        <v>938</v>
-      </c>
-      <c r="E101" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F101" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G101" s="16" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="20" t="s">
-        <v>940</v>
-      </c>
-      <c r="B102" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="C102" s="20" t="s">
-        <v>574</v>
-      </c>
-      <c r="D102" s="16" t="s">
-        <v>941</v>
-      </c>
-      <c r="E102" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F102" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="G102" s="16" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="20" t="s">
-        <v>943</v>
-      </c>
-      <c r="B103" s="20" t="s">
-        <v>600</v>
-      </c>
-      <c r="C103" s="20" t="s">
-        <v>944</v>
-      </c>
-      <c r="D103" s="16" t="s">
-        <v>945</v>
-      </c>
-      <c r="E103" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F103" s="20" t="s">
-        <v>615</v>
-      </c>
-      <c r="G103" s="16" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="20" t="s">
-        <v>947</v>
-      </c>
-      <c r="B104" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="C104" s="20" t="s">
-        <v>948</v>
-      </c>
-      <c r="D104" s="16" t="s">
-        <v>949</v>
-      </c>
-      <c r="E104" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F104" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G104" s="16" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="20" t="s">
-        <v>951</v>
-      </c>
-      <c r="B105" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="C105" s="20" t="s">
-        <v>952</v>
-      </c>
-      <c r="D105" s="16" t="s">
-        <v>953</v>
-      </c>
-      <c r="E105" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F105" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G105" s="16" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="20" t="s">
-        <v>955</v>
-      </c>
-      <c r="B106" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C106" s="20" t="s">
-        <v>956</v>
-      </c>
-      <c r="D106" s="16" t="s">
-        <v>957</v>
-      </c>
-      <c r="E106" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F106" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G106" s="16" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="20" t="s">
-        <v>959</v>
-      </c>
-      <c r="B107" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C107" s="20" t="s">
-        <v>960</v>
-      </c>
-      <c r="D107" s="16" t="s">
-        <v>961</v>
-      </c>
-      <c r="E107" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F107" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G107" s="16" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="20" t="s">
-        <v>963</v>
-      </c>
-      <c r="B108" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C108" s="20" t="s">
-        <v>964</v>
-      </c>
-      <c r="D108" s="16" t="s">
-        <v>965</v>
-      </c>
-      <c r="E108" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F108" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G108" s="16" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="20" t="s">
-        <v>967</v>
-      </c>
-      <c r="B109" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C109" s="20" t="s">
-        <v>968</v>
-      </c>
-      <c r="D109" s="16" t="s">
-        <v>969</v>
-      </c>
-      <c r="E109" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F109" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G109" s="16" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="147" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="20" t="s">
-        <v>971</v>
-      </c>
-      <c r="B110" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="C110" s="20" t="s">
-        <v>972</v>
-      </c>
-      <c r="D110" s="16" t="s">
-        <v>973</v>
-      </c>
-      <c r="E110" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F110" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G110" s="16" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="20" t="s">
-        <v>975</v>
-      </c>
-      <c r="B111" s="20" t="s">
-        <v>500</v>
-      </c>
-      <c r="C111" s="20" t="s">
-        <v>976</v>
-      </c>
-      <c r="D111" s="16" t="s">
-        <v>977</v>
-      </c>
-      <c r="E111" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F111" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G111" s="16" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="20" t="s">
-        <v>979</v>
-      </c>
-      <c r="B112" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="C112" s="20" t="s">
-        <v>980</v>
-      </c>
-      <c r="D112" s="16" t="s">
-        <v>981</v>
-      </c>
-      <c r="E112" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F112" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G112" s="16" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="20" t="s">
-        <v>983</v>
-      </c>
-      <c r="B113" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="C113" s="20" t="s">
-        <v>984</v>
-      </c>
-      <c r="D113" s="16" t="s">
-        <v>985</v>
-      </c>
-      <c r="E113" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F113" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G113" s="16" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="20" t="s">
-        <v>987</v>
-      </c>
-      <c r="B114" s="20" t="s">
-        <v>532</v>
-      </c>
-      <c r="C114" s="20" t="s">
-        <v>988</v>
-      </c>
-      <c r="D114" s="16" t="s">
-        <v>989</v>
-      </c>
-      <c r="E114" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F114" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G114" s="16" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="20" t="s">
-        <v>991</v>
-      </c>
-      <c r="B115" s="20" t="s">
+      <c r="C131" s="21" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D131" s="16" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E131" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F131" s="21" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G131" s="16" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="21" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B132" s="21" t="s">
+        <v>536</v>
+      </c>
+      <c r="C132" s="21" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D132" s="16" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E132" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F132" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G132" s="16" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="21" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B133" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="C115" s="20" t="s">
-        <v>992</v>
-      </c>
-      <c r="D115" s="16" t="s">
-        <v>993</v>
-      </c>
-      <c r="E115" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F115" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G115" s="16" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="20" t="s">
-        <v>995</v>
-      </c>
-      <c r="B116" s="20" t="s">
-        <v>532</v>
-      </c>
-      <c r="C116" s="20" t="s">
-        <v>996</v>
-      </c>
-      <c r="D116" s="16" t="s">
-        <v>997</v>
-      </c>
-      <c r="E116" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F116" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G116" s="16" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="20" t="s">
-        <v>999</v>
-      </c>
-      <c r="B117" s="20" t="s">
+      <c r="C133" s="21" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D133" s="16" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E133" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F133" s="21" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G133" s="16" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="21" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B134" s="21" t="s">
+        <v>552</v>
+      </c>
+      <c r="C134" s="21" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D134" s="16" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E134" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="F134" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="G134" s="16" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="21" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B135" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="C117" s="20" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D117" s="16" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E117" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F117" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G117" s="16" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="20" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B118" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C118" s="20" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D118" s="16" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E118" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F118" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G118" s="16" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="20" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B119" s="20" t="s">
-        <v>532</v>
-      </c>
-      <c r="C119" s="20" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D119" s="16" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E119" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F119" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G119" s="16" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="20" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B120" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C120" s="20" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D120" s="16" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E120" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F120" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G120" s="16" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="20" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B121" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C121" s="20" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D121" s="16" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E121" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F121" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G121" s="16" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="20" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B122" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C122" s="20" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D122" s="16" t="s">
-        <v>1021</v>
-      </c>
-      <c r="E122" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F122" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G122" s="16" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="20" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B123" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C123" s="20" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D123" s="16" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E123" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="F123" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G123" s="16" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="20" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B124" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C124" s="20" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D124" s="16" t="s">
-        <v>1029</v>
-      </c>
-      <c r="E124" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F124" s="20" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G124" s="16" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="20" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B125" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C125" s="20" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D125" s="16" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E125" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F125" s="20" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G125" s="16" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="20" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B126" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C126" s="20" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D126" s="16" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E126" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F126" s="20" t="s">
-        <v>1039</v>
-      </c>
-      <c r="G126" s="16" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="20" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B127" s="20" t="s">
-        <v>532</v>
-      </c>
-      <c r="C127" s="20" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D127" s="16" t="s">
-        <v>1043</v>
-      </c>
-      <c r="E127" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F127" s="20" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G127" s="16" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="20" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B128" s="20" t="s">
-        <v>532</v>
-      </c>
-      <c r="C128" s="20" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D128" s="16" t="s">
+      <c r="C135" s="21" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D135" s="16" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E135" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F135" s="21" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G135" s="16" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="21" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B136" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="C136" s="21" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D136" s="16" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E136" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="F136" s="21" t="s">
         <v>1047</v>
       </c>
-      <c r="E128" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F128" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="G128" s="16" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="20" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B129" s="20" t="s">
-        <v>532</v>
-      </c>
-      <c r="C129" s="20" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D129" s="16" t="s">
-        <v>1051</v>
-      </c>
-      <c r="E129" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F129" s="20" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G129" s="16" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="20" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B130" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C130" s="20" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D130" s="16" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E130" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="F130" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="G130" s="16" t="s">
-        <v>1056</v>
+      <c r="G136" s="16" t="s">
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -10404,7 +10771,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
@@ -10416,12 +10783,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>1057</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1058</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10429,16 +10796,16 @@
         <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1059</v>
+        <v>1103</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1060</v>
+        <v>1104</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1061</v>
+        <v>1105</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1062</v>
+        <v>1106</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>22</v>
@@ -10446,402 +10813,402 @@
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1063</v>
+        <v>1107</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1064</v>
+        <v>1108</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>1065</v>
+        <v>1109</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>1066</v>
+        <v>1110</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1067</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>676</v>
+        <v>1111</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1068</v>
+        <v>1112</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1069</v>
+        <v>1113</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1070</v>
+        <v>1114</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1071</v>
+        <v>1115</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>1073</v>
+        <v>1116</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1074</v>
+        <v>1118</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>1075</v>
+        <v>1119</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>1076</v>
+        <v>1120</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>1077</v>
+        <v>1121</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>615</v>
+        <v>1122</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1079</v>
+        <v>1123</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>1080</v>
+        <v>1124</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>1081</v>
+        <v>1125</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>1082</v>
+        <v>1126</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>615</v>
+        <v>1127</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1084</v>
+        <v>1128</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>1085</v>
+        <v>1129</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>1086</v>
+        <v>1130</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1087</v>
+        <v>1131</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1088</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>676</v>
+        <v>1132</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1089</v>
+        <v>1133</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1085</v>
+        <v>1129</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>1090</v>
+        <v>1134</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>1091</v>
+        <v>1135</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>676</v>
+        <v>1136</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1093</v>
+        <v>1137</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>1094</v>
+        <v>1138</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>1095</v>
+        <v>1139</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1096</v>
+        <v>1140</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>1073</v>
+        <v>1141</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1098</v>
+        <v>1142</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>1099</v>
+        <v>1143</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1100</v>
+        <v>1144</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>1101</v>
+        <v>1145</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1102</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>676</v>
+        <v>1146</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>1094</v>
+      <c r="A13" s="21" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>1138</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>1104</v>
+        <v>1148</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>1106</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>676</v>
+        <v>1149</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>1099</v>
+      <c r="A14" s="21" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>1143</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>1108</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>1110</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>1064</v>
-      </c>
       <c r="C16" s="16" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F16" s="21" t="s">
         <v>1117</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>1073</v>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>1085</v>
+      <c r="A17" s="21" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>1129</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>1121</v>
+        <v>1165</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>676</v>
+        <v>1166</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>1094</v>
+      <c r="A18" s="21" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>1138</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>1125</v>
+        <v>1169</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>676</v>
+        <v>1170</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
-        <v>1128</v>
-      </c>
-      <c r="B19" s="20" t="s">
+      <c r="A19" s="21" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B24" s="21" t="s">
         <v>1129</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>1132</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
-        <v>1133</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>1136</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>1137</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>1140</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>1141</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>1146</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>1147</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>1152</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>1085</v>
-      </c>
       <c r="C24" s="16" t="s">
-        <v>1154</v>
+        <v>1198</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>1155</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>676</v>
+        <v>1199</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>693</v>
       </c>
     </row>
   </sheetData>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -947,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="22" min="1" max="1"/>
@@ -1824,13 +1824,13 @@
       </c>
       <c r="E28" s="35" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F28" s="35" t="n"/>
       <c r="G28" s="36" t="inlineStr">
         <is>
-          <t>Requires UUID keys (0.3).</t>
+          <t>Built 2026-09-18, V8 applied locally. Append-only record of every write to a replicated entity. Records THAT something changed - type, id, action, branch, time - and never what it now says: a payload column would put a patient's assessment into the one table a peer is allowed to read. Ordered by bigserial, not by timestamp, so a watermark is an exact cursor rather than a guess. The recorder is a JPA @EntityListeners callback consumed AFTER_COMMIT in REQUIRES_NEW, so it sits BELOW the code that writes - 'every write is recorded because the recorder is beneath the services' stays true as the system grows; 'we remembered to call it' decays silently. Allow-list is the privacy decision: Forms, PatientIntake, Demographics and User are deliberately NOT replicated.</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,11 @@
         </is>
       </c>
       <c r="F29" s="28" t="n"/>
-      <c r="G29" s="45" t="n"/>
+      <c r="G29" s="45" t="inlineStr">
+        <is>
+          <t>NEXT. Node registry: table `node` (node_id, name, base_url, branch_id, last_seen_at, last_watermark, state) and GET /api/v1/sync/hello. Auth is a DEDICATED shared secret, never user JWTs - sharing a JWT signing key across nodes means a compromise of either forges logins on both. This is the stage that makes A1's node cards real: an unreachable peer reads 'unreachable, last seen 14:02' rather than being drawn as offline. See claude/sprint3-sync-design.md.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="23">
       <c r="A30" s="37" t="inlineStr">
@@ -3956,17 +3960,17 @@
       </c>
       <c r="E88" s="40" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F88" s="40" t="inlineStr">
         <is>
-          <t>Liodoq</t>
+          <t>Niccolo</t>
         </is>
       </c>
       <c r="G88" s="36" t="inlineStr">
         <is>
-          <t>STARTED - 2 of 10 treatments now priced (Signature Massage 60 at PHP 500), entered through the new A4 Service menu tab rather than the seeder. 8 still unpriced; the assistant correctly says the price is not on file for those. CRITICAL PATH until all ten are in.</t>
+          <t>DONE - observed on the live admin screen 2026-09-18. Real prices throughout: Hilotin Signature 60 P549 / 90 P823, Basic 60 P849, Bone Setting 60 P1,500, Head 30 P400, Hiris 120 P1,499, and the combos. This closes the P0.00 revenue column that would have been the first thing a panelist saw in the reports demo.</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6106,7 @@
       </c>
       <c r="E146" s="44" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F146" s="44" t="inlineStr">
@@ -6112,7 +6116,7 @@
       </c>
       <c r="G146" s="45" t="inlineStr">
         <is>
-          <t>Opened 2026-09-17. Local builds green: V6 and V7 both applied, Started BackendApplication clean, ng build clean. NOT yet deployed and NOT yet exercised in a browser - see the test script in the session doc.</t>
+          <t>DEPLOYED 2026-09-18. Commit eb59b37 pushed, pg_dump taken first, then V6, V7 and V8 all applied on production in one rebuild - 'Successfully applied 3 migrations, now at version v8', Started BackendApplication in 18.8s. Frontend shipped with deploy-frontend.ps1. V6 backfilled every production therapist with all three specialties, so nothing that booked before the deploy stopped booking. Backend went first because the new pages call endpoints the server did not yet have; the reverse would have been a site of 404s.</t>
         </is>
       </c>
     </row>
@@ -6472,17 +6476,128 @@
       </c>
       <c r="E156" s="44" t="inlineStr">
         <is>
+          <t>Not a bug (withdrawn)</t>
+        </is>
+      </c>
+      <c r="F156" s="44" t="inlineStr">
+        <is>
+          <t>Liodoq</t>
+        </is>
+      </c>
+      <c r="G156" s="45" t="inlineStr">
+        <is>
+          <t>WITHDRAWN 2026-09-18. Claude's diagnosis was WRONG. The two 'Signature Massage' rows in the A7 report are almost certainly the SAME treatment at 60 and 90 minutes - two legitimate catalogue rows, not a duplicate. The assistant's own prompt already carries the rule ('Several treatments share a name at different lengths - always say the minutes with the name'); the REPORT does not. Superseded by 3.30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="147" customHeight="1" s="23">
+      <c r="A157" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="B157" s="44" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="C157" s="45" t="inlineStr">
+        <is>
+          <t>Smoke-test the deployed revisions on the live site</t>
+        </is>
+      </c>
+      <c r="D157" s="45" t="inlineStr">
+        <is>
+          <t>Admin sidebar shows Reports and Reminders; Reports generates and states its scope; Staff Queue has Move on a still-to-come row; a client's Your visits shows the cancellation deadline; the protocol page offers import, Signature sheet and Record the signature.</t>
+        </is>
+      </c>
+      <c r="E157" s="44" t="inlineStr">
+        <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F156" s="44" t="inlineStr">
+      <c r="F157" s="44" t="inlineStr">
         <is>
           <t>Liodoq</t>
         </is>
       </c>
-      <c r="G156" s="45" t="inlineStr">
-        <is>
-          <t>Found 2026-09-18 in the A7 report, which listed Signature Massage twice (2 visits / 40% and 1 visit / 20%). The report is correct - they are different ids. It now shows a short id beside a duplicated name, but that is a plaster. It also BLOCKS the protocol import, which refuses to guess which of two same-named services a rule belongs to.</t>
+      <c r="G157" s="45" t="inlineStr">
+        <is>
+          <t>Opened 2026-09-18 immediately after deploy. Local builds and a clean start are NOT the same as exercised in a browser against production data - B133 was found by a real client on the live site, not by a build. Hard-refresh with Ctrl+Shift+R first: the chunk filenames changed and a cached index.html asks for files that no longer exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="147" customHeight="1" s="23">
+      <c r="A158" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B158" s="44" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C158" s="45" t="inlineStr">
+        <is>
+          <t>Show the duration wherever a treatment is named in reports and the protocol import</t>
+        </is>
+      </c>
+      <c r="D158" s="45" t="inlineStr">
+        <is>
+          <t>A7 lists 'Signature Massage' twice because 60 and 90 minutes are separate rows. Show minutes beside the name, and drop the short-id plaster added in 1.26. The protocol import must also stop REFUSING same-named services - it should disambiguate by duration instead.</t>
+        </is>
+      </c>
+      <c r="E158" s="44" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F158" s="44" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G158" s="45" t="inlineStr">
+        <is>
+          <t>Opened 2026-09-18, replacing the withdrawn 0.32. Claude told Liodoq to deactivate one of the two rows; that was wrong advice from an incomplete view of the catalogue. IMPORTANT: the protocol import currently refuses to guess between two same-named services, which now blocks legitimate rules for every treatment sold at two lengths. That refusal was right in principle and wrong in this catalogue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="147" customHeight="1" s="23">
+      <c r="A159" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B159" s="44" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C159" s="45" t="inlineStr">
+        <is>
+          <t>Combo treatments sold as their own catalogue rows</t>
+        </is>
+      </c>
+      <c r="D159" s="45" t="inlineStr">
+        <is>
+          <t>Bone Setting + Signature Massage 120 min P2,000; Therapeutic + Hotstone &amp; Ventosa 120 min P1,299; Hiris + Ventosa 120 min P1,899, and others. Ventosa, Hotstone and Suob exist withdrawn and unpriced as modifiers.</t>
+        </is>
+      </c>
+      <c r="E159" s="44" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F159" s="44" t="inlineStr">
+        <is>
+          <t>Niccolo</t>
+        </is>
+      </c>
+      <c r="G159" s="45" t="inlineStr">
+        <is>
+          <t>Observed live 2026-09-18. Closes B74. Solved WITHOUT a composition feature: each combo is one Massage row with its own duration and price, so the booking engine, the 30-minute slot grid and priceAtBooking all work unchanged, and the duration is stated rather than derived from two parts. The right call for this project.</t>
         </is>
       </c>
     </row>
@@ -9290,12 +9405,12 @@
       </c>
       <c r="F77" s="44" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G77" s="45" t="inlineStr">
         <is>
-          <t>Schema gap on the scale of the SS H items. Options: an add-on join table, or a composite service row per combo. Needs a decision before UAT.</t>
+          <t>Fixed 2026-09-18 by Niccolo - each combo is its own catalogue row with an explicit duration and price. No composition logic was needed.</t>
         </is>
       </c>
     </row>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -947,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="22" min="1" max="1"/>
@@ -6598,6 +6598,43 @@
       <c r="G159" s="45" t="inlineStr">
         <is>
           <t>Observed live 2026-09-18. Closes B74. Solved WITHOUT a composition feature: each combo is one Massage row with its own duration and price, so the booking engine, the 30-minute slot grid and priceAtBooking all work unchanged, and the duration is stated rather than derived from two parts. The right call for this project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="147" customHeight="1" s="23">
+      <c r="A160" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="B160" s="44" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="C160" s="45" t="inlineStr">
+        <is>
+          <t>Decide whether the admin console gets its own hostname</t>
+        </is>
+      </c>
+      <c r="D160" s="45" t="inlineStr">
+        <is>
+          <t>hilotspa-admin.duckdns.org. Adding it is one entry in SITE_HOST and FRONTEND_ORIGIN - the app and API are unchanged.</t>
+        </is>
+      </c>
+      <c r="E160" s="44" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F160" s="44" t="inlineStr">
+        <is>
+          <t>Liodoq</t>
+        </is>
+      </c>
+      <c r="G160" s="45" t="inlineStr">
+        <is>
+          <t>PARKED by Liodoq 2026-09-18, to revisit after node 2. The caveat to weigh then: a separate hostname is PRESENTATION, not protection. Same bundle, same API, so /admin still resolves on the branch hostname and access is decided by the role in the JWT, not by the name typed. Making it mean something requires Caddy refusing /admin/* on the public host, which is doable but buys little while the API is shared.</t>
         </is>
       </c>
     </row>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -947,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="22" min="1" max="1"/>
@@ -1560,13 +1560,17 @@
       </c>
       <c r="E20" s="35" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" s="35" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
       <c r="G20" s="36" t="inlineStr">
         <is>
-          <t>SUPERSEDED by 2.37, 2026-08-30. Process Rule #4 needed a guarantee that two transactions cannot award the same therapist or room; that guarantee now lives in Postgres as EXCLUDE USING gist, partial on blocking statuses, half-open ranges. A database constraint is strictly stronger than a Redis lock - it cannot be bypassed by a caller that forgets to take it, and it survives a cache restart. Marked N/A rather than Not Started so the sprint total is not understated at the defence.</t>
+          <t>DONE 2026-09-18 and LIVE IN PRODUCTION - verified with a real hold key on the server. Reopened from N/A after Liodoq pushed back on dropping Redis. Claude's first answer was wrong in scope: it argued against Redis as a lock around the booking WRITE, where the V2 EXCLUDE constraints already make double-booking impossible. The actual gap is BEFORE a row exists - between the assistant settling a time and the client choosing a therapist, where there is nothing to constrain and the assistant has been saying 'na-hold na po' about nothing (AssistantServiceImpl even carries a claimsHold() regex to detect the model saying it). A TTL hold is the right tool and Postgres is the wrong one: ephemeral, high-churn, self-expiring. Sorted set per (branch, hour), expiry in the score, pruned on read - no cleanup job, no KEYS scan. capacityAt() replaced the boolean anyFree() because one hesitating client must not empty an hour at a branch with five therapists. Redis unreachable = no hold and booking proceeds exactly as before, so NFR#1 is preserved.</t>
         </is>
       </c>
     </row>
@@ -6635,6 +6639,43 @@
       <c r="G160" s="45" t="inlineStr">
         <is>
           <t>PARKED by Liodoq 2026-09-18, to revisit after node 2. The caveat to weigh then: a separate hostname is PRESENTATION, not protection. Same bundle, same API, so /admin still resolves on the branch hostname and access is decided by the role in the JWT, not by the name typed. Making it mean something requires Caddy refusing /admin/* on the public host, which is doable but buys little while the API is shared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="147" customHeight="1" s="23">
+      <c r="A161" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="B161" s="44" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="C161" s="45" t="inlineStr">
+        <is>
+          <t>REDIS_HOST needed a compose override, like DB_HOST and N8N_WEBHOOK_URL</t>
+        </is>
+      </c>
+      <c r="D161" s="45" t="inlineStr">
+        <is>
+          <t>.env says localhost, which is right for run.ps1 and is the BACKEND ITSELF inside the compose network. Added REDIS_HOST: redis and REDIS_PORT: 6379 to the backend's environment block.</t>
+        </is>
+      </c>
+      <c r="E161" s="44" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F161" s="44" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G161" s="45" t="inlineStr">
+        <is>
+          <t>Third instance of one pattern on 2026-09-18, and the comment block in compose.yaml already documented the other two. Claude added a variable that needed the same treatment and did not give it. Compounded by SlotHoldService logging every failure at DEBUG - 'degrade silently' turned a misconfiguration invisible: every hold was a refused connection and every signal said healthy. Fixed by warning ONCE at WARN then falling back to DEBUG. This is B60's lesson repeating: a fallback that cannot tell 'not attempted' from 'failed' hides the failures you most need to see.</t>
         </is>
       </c>
     </row>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -947,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="22" min="1" max="1"/>
@@ -1933,7 +1933,7 @@
       <c r="F31" s="28" t="n"/>
       <c r="G31" s="45" t="inlineStr">
         <is>
-          <t>Half of it is now enforced, and it is the half that can be. 2026-08-30: a therapist and a room each belong to exactly one branch (schema), and Flyway migration V2 adds EXCLUDE constraints so the database itself refuses an overlapping write. Within a node, single-writer is a mechanism rather than a convention. What remains is the cross-node half - a node refusing to write a resource it does not own - which needs the node registry (3.2) to exist first.</t>
+          <t>Half of it is now enforced, and it is the half that can be. 2026-08-30: a therapist and a room each belong to exactly one branch (schema), and Flyway migration V2 adds EXCLUDE constraints so the database itself refuses an overlapping write. Within a node, single-writer is a mechanism rather than a convention. What remains is the cross-node half - a node refusing to write a resource it does not own - which needs the node registry (3.2) to exist first. | 2026-09-18: advanced by 3.31. The data model already made two nodes unable to write the same row; the CLIENT was still choosing the wrong partition. See B137.</t>
         </is>
       </c>
     </row>
@@ -2125,13 +2125,13 @@
       </c>
       <c r="E37" s="28" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F37" s="28" t="n"/>
       <c r="G37" s="45" t="inlineStr">
         <is>
-          <t>Research locale names only one branch. See Defense Risks R5.</t>
+          <t>Node 2 live 2026-09-18: hilotspa-daraga.duckdns.org on its own EC2 (t3.small, Ubuntu 26.04, 2 GB + 2 GB swap, Elastic IP), restored from a pg_dump of node 1, own JWT_SECRET and DB password, certificate obtained first attempt, Redis hold verified. Nothing was deleted anywhere - node 2 HOLDS both branches and WRITES only Daraga. Traps hit and recorded: the security group's rules went into the OUTBOUND list (SSH timed out AND outbound UDP 53 was blocked, so DNS would have failed next); Docker created the bind-mount source ~/hilotSpa/site as ROOT because it did not exist, so the frontend swap failed on an empty site. Runbook: node2-clone-and-split-RUNBOOK.md.</t>
         </is>
       </c>
     </row>
@@ -6676,6 +6676,80 @@
       <c r="G161" s="45" t="inlineStr">
         <is>
           <t>Third instance of one pattern on 2026-09-18, and the comment block in compose.yaml already documented the other two. Claude added a variable that needed the same treatment and did not give it. Compounded by SlotHoldService logging every failure at DEBUG - 'degrade silently' turned a misconfiguration invisible: every hold was a refused connection and every signal said healthy. Fixed by warning ONCE at WARN then falling back to DEBUG. This is B60's lesson repeating: a fallback that cannot tell 'not attempted' from 'failed' hides the failures you most need to see.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B162" s="44" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="C162" s="45" t="inlineStr">
+        <is>
+          <t>Node identity - each node names and writes for its own branch</t>
+        </is>
+      </c>
+      <c r="D162" s="45" t="inlineStr">
+        <is>
+          <t>GET /api/v1/public/node returns nodeId, nodeName, branchId, branchName from NODE_BRANCH_ID. Shared NodeStore on the client. The top bar, landing hero, contact, about and the Appendix C signature sheet all read it instead of a literal string, and the assessment files against it instead of branches[0]. The nightly reminder run is scoped to it.</t>
+        </is>
+      </c>
+      <c r="E162" s="44" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F162" s="44" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G162" s="45" t="inlineStr">
+        <is>
+          <t>Built and deployed 2026-09-18 after node 2 went up and the Daraga site announced itself as Bulan. Closes B137. The startup line "Node X writes for branch Y" is the whole change, verifiable in one grep. A node that declares no branch keeps the old behaviour exactly - a single-node deployment is legitimate - but says so at WARN, because a silent fallback that cannot distinguish "not configured" from "configured" is the B60/0.35 lesson again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B163" s="44" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="C163" s="45" t="inlineStr">
+        <is>
+          <t>Clamp the MANUAL reminder run to the node's own branch</t>
+        </is>
+      </c>
+      <c r="D163" s="45" t="inlineStr">
+        <is>
+          <t>NotificationController.run() uses scopeOf(branchId), which returns null - every branch - for an ADMIN who selects none. The nightly job is scoped by 3.31; the button is not.</t>
+        </is>
+      </c>
+      <c r="E163" s="44" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="F163" s="44" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G163" s="45" t="inlineStr">
+        <is>
+          <t>Opened 2026-09-18. Node 2 keeps MAIL_HOST BLANK until this lands, or an administrator pressing Run reminders there will re-send what node 1 already sent - notification_log is deliberately not replicated, so node 2 cannot know. Needs a product decision first: should an admin on the Daraga node be ABLE to send Bulan reminders at all? Recommendation is no, on the same partitioning argument.</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -11783,6 +11857,80 @@
       <c r="G139" s="45" t="inlineStr">
         <is>
           <t>Fixed 2026-09-18. The page only knew about the STAFF token; an ADMIN inside a branch context is equally scoped. Same family as B101.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="44" t="inlineStr">
+        <is>
+          <t>B137</t>
+        </is>
+      </c>
+      <c r="B140" s="44" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="C140" s="44" t="inlineStr">
+        <is>
+          <t>frontend - review.ts, app-nav, landing, about, contact, protocol-sheet</t>
+        </is>
+      </c>
+      <c r="D140" s="45" t="inlineStr">
+        <is>
+          <t>A customer has no token and therefore no branch, so the assessment fell back to branches[0] - Bulan, alphabetically. On two nodes that meant a client booking on the DARAGA node filed a BULAN appointment. The branch was also a literal string in six templates, including the Appendix C sheet a practitioner signs.</t>
+        </is>
+      </c>
+      <c r="E140" s="44" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F140" s="44" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G140" s="45" t="inlineStr">
+        <is>
+          <t>Found 2026-09-18 within an hour of node 2 going live: the Daraga site introduced itself as Bulan. Harmless while one node existed, which is why it survived review. Single-writer-per-partition is the property the whole architecture rests on and a DEFAULT was breaking it at the point of entry - the database could not catch it, because a Bulan appointment written by node 2 is a perfectly valid row. Fixed by 3.31. The signed-sheet instance was the worst: a signed protocol table naming the wrong branch asserts that somebody approved rules for a place they never approved them for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="44" t="inlineStr">
+        <is>
+          <t>B138</t>
+        </is>
+      </c>
+      <c r="B141" s="44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C141" s="44" t="inlineStr">
+        <is>
+          <t>node 1 .env</t>
+        </is>
+      </c>
+      <c r="D141" s="45" t="inlineStr">
+        <is>
+          <t>FRONTEND_ORIGIN appears TWICE. Docker Compose takes the last occurrence, so the node works - but anyone editing the first one, which is where you would look, changes nothing.</t>
+        </is>
+      </c>
+      <c r="E141" s="44" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F141" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G141" s="45" t="inlineStr">
+        <is>
+          <t>Found 2026-09-18 while listing key names for node 2. Left from the multi-origin CORS change earlier the same day: the new value was appended instead of replacing the old. Collapse to one line next time node 1 .env is touched.</t>
         </is>
       </c>
     </row>

--- a/HilotSpa_ThesisTracker.xlsx
+++ b/HilotSpa_ThesisTracker.xlsx
@@ -947,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="22" min="1" max="1"/>
@@ -1861,13 +1861,13 @@
       </c>
       <c r="E29" s="28" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F29" s="28" t="n"/>
       <c r="G29" s="45" t="inlineStr">
         <is>
-          <t>NEXT. Node registry: table `node` (node_id, name, base_url, branch_id, last_seen_at, last_watermark, state) and GET /api/v1/sync/hello. Auth is a DEDICATED shared secret, never user JWTs - sharing a JWT signing key across nodes means a compromise of either forges logins on both. This is the stage that makes A1's node cards real: an unreachable peer reads 'unreachable, last seen 14:02' rather than being drawn as offline. See claude/sprint3-sync-design.md.</t>
+          <t>NEXT. Node registry: table `node` (node_id, name, base_url, branch_id, last_seen_at, last_watermark, state) and GET /api/v1/sync/hello. Auth is a DEDICATED shared secret, never user JWTs - sharing a JWT signing key across nodes means a compromise of either forges logins on both. This is the stage that makes A1's node cards real: an unreachable peer reads 'unreachable, last seen 14:02' rather than being drawn as offline. See claude/sprint3-sync-design.md. | Built and deployed 2026-09-19. V9 node table; each node writes its own row and polls each configured peer every 30s. Peers are configured as URLs and IDENTITY IS DISCOVERED - a node id in config too means two places can disagree about a name. /api/v1/sync/** is guarded by SyncTokenFilter with a shared secret that DEFAULTS CLOSED, because both nodes publish 443 to the internet for ACME. Constant-time comparison. First run failed 401 on both sides: the generate command had been run on both nodes, producing two different secrets - diagnosed by comparing sha256 fingerprints without either of us seeing the value.</t>
         </is>
       </c>
     </row>
@@ -1894,13 +1894,13 @@
       </c>
       <c r="E30" s="28" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F30" s="28" t="n"/>
       <c r="G30" s="45" t="inlineStr">
         <is>
-          <t>FR#3</t>
+          <t>FR#3 | Built and deployed 2026-09-19. GET /sync/changes?since= returns only rows this node ORIGINATED; GET /sync/appointments?ids= answers only about ids the caller was already told changed - there is no 'list everything'. Appointments cross; accounts, assessments and pain maps are not in sync_log at all, so the puller could not fetch them if it tried. Native ON CONFLICT (id) DO UPDATE rather than save(): the id is @GeneratedValue, and merge on a row absent from this database would let the generator assign a NEW id - silent unbounded duplication on every pull. ReplicationContext (ThreadLocal) stops an applied change being re-advertised, which would otherwise make the two nodes pass the same row back and forth for ever.</t>
         </is>
       </c>
     </row>
@@ -1927,13 +1927,13 @@
       </c>
       <c r="E31" s="28" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F31" s="28" t="n"/>
       <c r="G31" s="45" t="inlineStr">
         <is>
-          <t>Half of it is now enforced, and it is the half that can be. 2026-08-30: a therapist and a room each belong to exactly one branch (schema), and Flyway migration V2 adds EXCLUDE constraints so the database itself refuses an overlapping write. Within a node, single-writer is a mechanism rather than a convention. What remains is the cross-node half - a node refusing to write a resource it does not own - which needs the node registry (3.2) to exist first. | 2026-09-18: advanced by 3.31. The data model already made two nodes unable to write the same row; the CLIENT was still choosing the wrong partition. See B137.</t>
+          <t>Half of it is now enforced, and it is the half that can be. 2026-08-30: a therapist and a room each belong to exactly one branch (schema), and Flyway migration V2 adds EXCLUDE constraints so the database itself refuses an overlapping write. Within a node, single-writer is a mechanism rather than a convention. What remains is the cross-node half - a node refusing to write a resource it does not own - which needs the node registry (3.2) to exist first. | 2026-09-18: advanced by 3.31. The data model already made two nodes unable to write the same row; the CLIENT was still choosing the wrong partition. See B137. | Done 2026-09-19. Now enforced in three places: the data model (a therapist and a room belong to one branch), createForm (the node decides a customer's branch, not the request body - B139), and the reminder clamp (3.32). The client-side fix alone was insufficient: a cached bundle, a stale tab or curl would have bypassed it.</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E112" s="44" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F112" s="44" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="G112" s="45" t="inlineStr">
         <is>
-          <t>~30 min and it is the prerequisite for every hosting route. Also removes a whole class of defence-day failure: one thing to start instead of two.</t>
+          <t>~30 min and it is the prerequisite for every hosting route. Also removes a whole class of defence-day failure: one thing to start instead of two. | Done - Caddy serves the bundle and proxies /api on both nodes.</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="E113" s="44" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F113" s="44" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G113" s="45" t="inlineStr">
         <is>
-          <t>Needed for a real URL by either route.</t>
+          <t>Needed for a real URL by either route. | Done - Caddy with automatic Let's Encrypt on both nodes; SITE_HOST comes from the environment, never the tracked Caddyfile.</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E114" s="44" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F114" s="44" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G114" s="45" t="inlineStr">
         <is>
-          <t>The panel has asked for a real URL. NOTE: AWS changed the free tier - accounts after 15 Jul 2025 get $100 credits for 12 months, not 750 free hours, and a Free Plan account auto-closes when they run out.</t>
+          <t>The panel has asked for a real URL. NOTE: AWS changed the free tier - accounts after 15 Jul 2025 get $100 credits for 12 months, not 750 free hours, and a Free Plan account auto-closes when they run out. | Done - two EC2 t3.small in ap-southeast-1, both on the same account.</t>
         </is>
       </c>
     </row>
@@ -6739,17 +6739,91 @@
       </c>
       <c r="E163" s="44" t="inlineStr">
         <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F163" s="44" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G163" s="45" t="inlineStr">
+        <is>
+          <t>Opened 2026-09-18. Node 2 keeps MAIL_HOST BLANK until this lands, or an administrator pressing Run reminders there will re-send what node 1 already sent - notification_log is deliberately not replicated, so node 2 cannot know. Needs a product decision first: should an admin on the Daraga node be ABLE to send Bulan reminders at all? Recommendation is no, on the same partitioning argument. | Done 2026-09-19. sendScope() clamps both send paths to the branch this node owns; an admin asking for every branch gets a 409 naming which machine to use. Reads are deliberately NOT clamped - the row is already in this database; mailing its client is the thing that leaves the building. A8 states which branch the node sends for before anybody presses anything. MAIL_HOST restored on node 2 once node 1 was clamped first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B164" s="44" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="C164" s="45" t="inlineStr">
+        <is>
+          <t>Planned therapist leave, and the bookings it breaks</t>
+        </is>
+      </c>
+      <c r="D164" s="45" t="inlineStr">
+        <is>
+          <t>V10 therapist_leave: a dated, inclusive range entered in advance. Filtered per-day inside availability() and enforced in freeTherapists(), which is the gate the WRITE passes through. Recording leave is never refused because of existing bookings - it answers with the clashing visits by name and time.</t>
+        </is>
+      </c>
+      <c r="E164" s="44" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F164" s="44" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G164" s="45" t="inlineStr">
+        <is>
+          <t>Built 2026-09-19 at the adviser's question. The system had therapist.status (right-now, today only) and therapist.active (has left, for ever) and nothing in between. Deliberately does NOT auto-cancel: the client still wants the treatment, there is no cancellation email in this system, and swapping the practitioner on a bone-setting appointment is a real change rather than a clerical one. KNOWN WEAKNESS raised by the adviser: the clash list lives on the leave record, so it can be missed. The day-sheet warning that closes that hole is task 3.34.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B165" s="44" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="C165" s="45" t="inlineStr">
+        <is>
+          <t>Mark bookings whose therapist is on leave, on the day sheet and queue</t>
+        </is>
+      </c>
+      <c r="D165" s="45" t="inlineStr">
+        <is>
+          <t>Surface the clash where staff already look, rather than only on the leave record.</t>
+        </is>
+      </c>
+      <c r="E165" s="44" t="inlineStr">
+        <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F163" s="44" t="inlineStr">
+      <c r="F165" s="44" t="inlineStr">
         <is>
           <t>Claude</t>
         </is>
       </c>
-      <c r="G163" s="45" t="inlineStr">
-        <is>
-          <t>Opened 2026-09-18. Node 2 keeps MAIL_HOST BLANK until this lands, or an administrator pressing Run reminders there will re-send what node 1 already sent - notification_log is deliberately not replicated, so node 2 cannot know. Needs a product decision first: should an admin on the Daraga node be ABLE to send Bulan reminders at all? Recommendation is no, on the same partitioning argument.</t>
+      <c r="G165" s="45" t="inlineStr">
+        <is>
+          <t>Opened 2026-09-19. This is what makes 3.33 defensible: flag-and-decide only works if somebody looks. Enter leave for three weeks ahead, nobody reopens that screen, and the client turns up to a therapist who is not there. ~45 minutes and it does not touch the availability path.</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -11931,6 +12005,154 @@
       <c r="G141" s="45" t="inlineStr">
         <is>
           <t>Found 2026-09-18 while listing key names for node 2. Left from the multi-origin CORS change earlier the same day: the new value was appended instead of replacing the old. Collapse to one line next time node 1 .env is touched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>B139</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>FormsServiceImpl.createForm</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>For a CUSTOMER, branchId was taken straight from the request body. A booking made on the Bulan site was filed against Daraga, because a frontend predating 3.31 falls back to branches[0] and the branch list comes back UNORDERED from the API.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Found 2026-09-19 by clicking through, not by reading code. The frontend fix shipped the night before was necessary and insufficient - single-writer-per-partition cannot depend on every client being current. Enforced at the writer now. Appointments inherit the form branch, so one change covers availability, the hold, the booking and the reminder. Trap worth remembering: on node 1 the OLD hardcoded "Bulan, Sorsogon" and the correct dynamic value are identical, so the screen Claude checked was the one screen that could not reveal the fault.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>B140</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>pages/home - customer landing</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>A visit on 20 Sep appears under BOTH "Your next visit" and "Past sessions" while it is still in the future.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Found 2026-09-19. Visible on the first screen a client sees, and on a screen the adviser will open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>B141</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>deploy-frontend.ps1</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>The swap deletes every file before copying the new build, so any browser tab open at that moment breaks with "Failed to fetch dynamically imported module: chunk-XXXX.js" the next time it navigates.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Hit repeatedly on 2026-09-19. Angular lazy chunks carry hashed names; a page holding the old index.html asks for chunks that no longer exist. Fix is to overlay the new build instead of deleting first, and prune old files later. Until then: hard refresh after every deploy, and DO NOT deploy while the adviser has the site open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>B142</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>.env on both nodes - MAIL_USERNAME</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>MAIL_USERNAME, MAIL_FROM and MAIL_REPLY_TO carried one extra "s" (kneadwellnesssspa@). Gmail rejected a username that does not exist, which is indistinguishable from a bad password on the admin screen.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Fixed 2026-09-19 after a long chase. Earlier causes in the same chain: MAIL_HOST set to the literal placeholder "&lt;the value from node 1&gt;" (Claude's fault for writing a pasteable placeholder - second time, after &lt;paste-a-key-here&gt; in Session 16), and a 19-character MAIL_PASSWORD. Settled only by talking to smtp.gmail.com directly with python3 and reading Google's own words instead of Spring's wrapper. LESSON: when an error message is generic, stop inferring and ask the system that is refusing.</t>
         </is>
       </c>
     </row>
